--- a/Data/raw/SD FACTORS AND FOOD WASTE QUANTITY.xlsx
+++ b/Data/raw/SD FACTORS AND FOOD WASTE QUANTITY.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b6a8a74c1ce5fdf/Desktop/thesis data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\project-waste\Data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11775127-30AC-4A1B-9CDB-F436CC588499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CC71F6-57B8-4616-9EFB-CC0E63AB1157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C7D7AED6-78B4-43ED-8990-65A9756CF315}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C7D7AED6-78B4-43ED-8990-65A9756CF315}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
   <si>
     <t>H.No.</t>
   </si>
@@ -74,42 +74,6 @@
     <t>Food Waste/Day/kg</t>
   </si>
   <si>
-    <t>ethra thavana cook cheyyum</t>
-  </si>
-  <si>
-    <t>അധികം വരുന്നതും ഭക്ഷ്യയോഗ്യമായതുമായ ഭക്ഷണം എങ്ങനെയാണ് കൈകാര്യം ചെയ്യുന്നത്?</t>
-  </si>
-  <si>
-    <t>ഫ്രിഡ്ജ് ഉപയോഗിക്കുന്നു</t>
-  </si>
-  <si>
-    <t>ഭക്ഷണം ശേഖരിച്ചു വെക്കാറില്ല</t>
-  </si>
-  <si>
-    <t>ഫ്രിഡ്ജിൽ സൂക്ഷിച്ച ആഹാര പദാർഥങ്ങൾ എത്ര ദിവസം വരെ ഉപയോഗിക്കും</t>
-  </si>
-  <si>
-    <t>ഒരു ദിവസം എത്ര തവണ ഭക്ഷണം പാകം ചെയ്യും?</t>
-  </si>
-  <si>
-    <t>1. ഫ്രിഡ്ജ് ഉപയോഗിക്കുന്നു, 2. ഭക്ഷണം ശേഖരിച്ചു വെക്കാറില്ല, 4. കളയും</t>
-  </si>
-  <si>
-    <t>2. ഭക്ഷണം ശേഖരിച്ചു വെക്കാറില്ല</t>
-  </si>
-  <si>
-    <t>1. ഫ്രിഡ്ജ് ഉപയോഗിക്കുന്നു, 4. കളയും</t>
-  </si>
-  <si>
-    <t>1. ഫ്രിഡ്ജ് ഉപയോഗിക്കുന്നു</t>
-  </si>
-  <si>
-    <t>2. ഭക്ഷണം ശേഖരിച്ചു വെക്കാറില്ല, 4. കളയും</t>
-  </si>
-  <si>
-    <t>1. ഫ്രിഡ്ജ് ഉപയോഗിക്കുന്നു, 2. ഭക്ഷണം ശേഖരിച്ചു വെക്കാറില്ല</t>
-  </si>
-  <si>
     <t>4. കളയും</t>
   </si>
   <si>
@@ -129,6 +93,18 @@
   </si>
   <si>
     <t>ല്ല</t>
+  </si>
+  <si>
+    <t>times of cooking</t>
+  </si>
+  <si>
+    <t>management of excess food</t>
+  </si>
+  <si>
+    <t>storing time in fridge</t>
+  </si>
+  <si>
+    <t>1, 2</t>
   </si>
 </sst>
 </file>
@@ -389,10 +365,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18805,26 +18777,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25692E9D-CE31-476C-8739-B3D21602F49F}">
-  <dimension ref="A1:C494"/>
+  <dimension ref="A1:C493"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="221.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12">
         <v>2</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>14</v>
+      <c r="B2" s="15">
+        <v>1</v>
       </c>
       <c r="C2" s="19"/>
     </row>
@@ -18832,8 +18804,8 @@
       <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>15</v>
+      <c r="B3" s="16">
+        <v>2</v>
       </c>
       <c r="C3" s="17"/>
     </row>
@@ -18841,8 +18813,8 @@
       <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>15</v>
+      <c r="B4" s="15">
+        <v>2</v>
       </c>
       <c r="C4" s="19"/>
     </row>
@@ -18850,8 +18822,8 @@
       <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>15</v>
+      <c r="B5" s="16">
+        <v>2</v>
       </c>
       <c r="C5" s="17"/>
     </row>
@@ -18859,8 +18831,8 @@
       <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>15</v>
+      <c r="B6" s="15">
+        <v>2</v>
       </c>
       <c r="C6" s="19"/>
     </row>
@@ -18868,8 +18840,8 @@
       <c r="A7" s="13">
         <v>2</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>15</v>
+      <c r="B7" s="16">
+        <v>2</v>
       </c>
       <c r="C7" s="17"/>
     </row>
@@ -18877,8 +18849,8 @@
       <c r="A8" s="12">
         <v>3</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>14</v>
+      <c r="B8" s="15">
+        <v>1</v>
       </c>
       <c r="C8" s="19"/>
     </row>
@@ -18886,8 +18858,8 @@
       <c r="A9" s="13">
         <v>1</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>14</v>
+      <c r="B9" s="16">
+        <v>1</v>
       </c>
       <c r="C9" s="17"/>
     </row>
@@ -18895,8 +18867,8 @@
       <c r="A10" s="12">
         <v>2</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>15</v>
+      <c r="B10" s="15">
+        <v>2</v>
       </c>
       <c r="C10" s="19"/>
     </row>
@@ -18904,8 +18876,8 @@
       <c r="A11" s="13">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>14</v>
+      <c r="B11" s="16">
+        <v>1</v>
       </c>
       <c r="C11" s="17"/>
     </row>
@@ -18913,8 +18885,8 @@
       <c r="A12" s="12">
         <v>2</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>15</v>
+      <c r="B12" s="15">
+        <v>2</v>
       </c>
       <c r="C12" s="19"/>
     </row>
@@ -18922,8 +18894,8 @@
       <c r="A13" s="13">
         <v>2</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>15</v>
+      <c r="B13" s="16">
+        <v>2</v>
       </c>
       <c r="C13" s="17"/>
     </row>
@@ -18931,8 +18903,8 @@
       <c r="A14" s="12">
         <v>2</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>15</v>
+      <c r="B14" s="15">
+        <v>2</v>
       </c>
       <c r="C14" s="19"/>
     </row>
@@ -18940,8 +18912,8 @@
       <c r="A15" s="13">
         <v>4</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>14</v>
+      <c r="B15" s="16">
+        <v>1</v>
       </c>
       <c r="C15" s="17"/>
     </row>
@@ -18949,8 +18921,8 @@
       <c r="A16" s="12">
         <v>3</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>14</v>
+      <c r="B16" s="15">
+        <v>1</v>
       </c>
       <c r="C16" s="19"/>
     </row>
@@ -18958,8 +18930,8 @@
       <c r="A17" s="13">
         <v>3</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>14</v>
+      <c r="B17" s="16">
+        <v>1</v>
       </c>
       <c r="C17" s="13">
         <v>2</v>
@@ -18969,8 +18941,8 @@
       <c r="A18" s="12">
         <v>3</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>15</v>
+      <c r="B18" s="15">
+        <v>2</v>
       </c>
       <c r="C18" s="12">
         <v>1</v>
@@ -18980,8 +18952,8 @@
       <c r="A19" s="13">
         <v>3</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>14</v>
+      <c r="B19" s="16">
+        <v>1</v>
       </c>
       <c r="C19" s="13">
         <v>2</v>
@@ -18991,8 +18963,8 @@
       <c r="A20" s="12">
         <v>3</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>15</v>
+      <c r="B20" s="15">
+        <v>2</v>
       </c>
       <c r="C20" s="12">
         <v>1</v>
@@ -19002,8 +18974,8 @@
       <c r="A21" s="13">
         <v>2</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>14</v>
+      <c r="B21" s="16">
+        <v>1</v>
       </c>
       <c r="C21" s="13">
         <v>1</v>
@@ -19013,8 +18985,8 @@
       <c r="A22" s="12">
         <v>2</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>15</v>
+      <c r="B22" s="15">
+        <v>2</v>
       </c>
       <c r="C22" s="12">
         <v>1</v>
@@ -19024,8 +18996,8 @@
       <c r="A23" s="13">
         <v>1</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>14</v>
+      <c r="B23" s="16">
+        <v>1</v>
       </c>
       <c r="C23" s="17"/>
     </row>
@@ -19033,8 +19005,8 @@
       <c r="A24" s="12">
         <v>2</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>14</v>
+      <c r="B24" s="15">
+        <v>1</v>
       </c>
       <c r="C24" s="19"/>
     </row>
@@ -19042,8 +19014,8 @@
       <c r="A25" s="13">
         <v>2</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>14</v>
+      <c r="B25" s="16">
+        <v>1</v>
       </c>
       <c r="C25" s="13">
         <v>1</v>
@@ -19053,8 +19025,8 @@
       <c r="A26" s="12">
         <v>2</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>14</v>
+      <c r="B26" s="15">
+        <v>1</v>
       </c>
       <c r="C26" s="12">
         <v>1</v>
@@ -19064,8 +19036,8 @@
       <c r="A27" s="13">
         <v>3</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>14</v>
+      <c r="B27" s="16">
+        <v>1</v>
       </c>
       <c r="C27" s="13">
         <v>1</v>
@@ -19075,8 +19047,8 @@
       <c r="A28" s="12">
         <v>1</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>14</v>
+      <c r="B28" s="15">
+        <v>1</v>
       </c>
       <c r="C28" s="12">
         <v>1</v>
@@ -19086,8 +19058,8 @@
       <c r="A29" s="13">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>15</v>
+      <c r="B29" s="16">
+        <v>2</v>
       </c>
       <c r="C29" s="13">
         <v>1</v>
@@ -19097,8 +19069,8 @@
       <c r="A30" s="12">
         <v>1</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>15</v>
+      <c r="B30" s="15">
+        <v>2</v>
       </c>
       <c r="C30" s="12">
         <v>1</v>
@@ -19108,8 +19080,8 @@
       <c r="A31" s="13">
         <v>1</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>15</v>
+      <c r="B31" s="16">
+        <v>2</v>
       </c>
       <c r="C31" s="13">
         <v>1</v>
@@ -19119,8 +19091,8 @@
       <c r="A32" s="12">
         <v>2</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>14</v>
+      <c r="B32" s="15">
+        <v>1</v>
       </c>
       <c r="C32" s="12">
         <v>2</v>
@@ -19130,8 +19102,8 @@
       <c r="A33" s="13">
         <v>1</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>14</v>
+      <c r="B33" s="16">
+        <v>1</v>
       </c>
       <c r="C33" s="13">
         <v>1</v>
@@ -19141,8 +19113,8 @@
       <c r="A34" s="12">
         <v>1</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>14</v>
+      <c r="B34" s="15">
+        <v>1</v>
       </c>
       <c r="C34" s="12">
         <v>1</v>
@@ -19152,8 +19124,8 @@
       <c r="A35" s="13">
         <v>2</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>14</v>
+      <c r="B35" s="16">
+        <v>1</v>
       </c>
       <c r="C35" s="13">
         <v>30</v>
@@ -19163,8 +19135,8 @@
       <c r="A36" s="12">
         <v>2</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>15</v>
+      <c r="B36" s="15">
+        <v>2</v>
       </c>
       <c r="C36" s="12">
         <v>1</v>
@@ -19174,8 +19146,8 @@
       <c r="A37" s="13">
         <v>3</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>14</v>
+      <c r="B37" s="16">
+        <v>1</v>
       </c>
       <c r="C37" s="13">
         <v>3</v>
@@ -19185,8 +19157,8 @@
       <c r="A38" s="12">
         <v>3</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>14</v>
+      <c r="B38" s="15">
+        <v>1</v>
       </c>
       <c r="C38" s="12">
         <v>1</v>
@@ -19196,8 +19168,8 @@
       <c r="A39" s="13">
         <v>2</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>15</v>
+      <c r="B39" s="16">
+        <v>2</v>
       </c>
       <c r="C39" s="13">
         <v>1</v>
@@ -19207,8 +19179,8 @@
       <c r="A40" s="12">
         <v>2</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>14</v>
+      <c r="B40" s="15">
+        <v>1</v>
       </c>
       <c r="C40" s="12">
         <v>1</v>
@@ -19218,8 +19190,8 @@
       <c r="A41" s="13">
         <v>2</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>15</v>
+      <c r="B41" s="16">
+        <v>2</v>
       </c>
       <c r="C41" s="13">
         <v>0</v>
@@ -19229,8 +19201,8 @@
       <c r="A42" s="12">
         <v>2</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>14</v>
+      <c r="B42" s="15">
+        <v>1</v>
       </c>
       <c r="C42" s="12">
         <v>1</v>
@@ -19240,8 +19212,8 @@
       <c r="A43" s="13">
         <v>3</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>15</v>
+      <c r="B43" s="16">
+        <v>2</v>
       </c>
       <c r="C43" s="13">
         <v>0</v>
@@ -19251,8 +19223,8 @@
       <c r="A44" s="12">
         <v>1</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>14</v>
+      <c r="B44" s="15">
+        <v>1</v>
       </c>
       <c r="C44" s="12">
         <v>1</v>
@@ -19262,8 +19234,8 @@
       <c r="A45" s="13">
         <v>1</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>14</v>
+      <c r="B45" s="16">
+        <v>1</v>
       </c>
       <c r="C45" s="13">
         <v>1</v>
@@ -19273,8 +19245,8 @@
       <c r="A46" s="12">
         <v>1</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>14</v>
+      <c r="B46" s="15">
+        <v>1</v>
       </c>
       <c r="C46" s="12">
         <v>1</v>
@@ -19291,8 +19263,8 @@
       <c r="A48" s="12">
         <v>4</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>15</v>
+      <c r="B48" s="15">
+        <v>2</v>
       </c>
       <c r="C48" s="12">
         <v>0</v>
@@ -19302,8 +19274,8 @@
       <c r="A49" s="13">
         <v>1</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>14</v>
+      <c r="B49" s="16">
+        <v>1</v>
       </c>
       <c r="C49" s="13">
         <v>2</v>
@@ -19313,8 +19285,8 @@
       <c r="A50" s="12">
         <v>2</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>14</v>
+      <c r="B50" s="15">
+        <v>1</v>
       </c>
       <c r="C50" s="12">
         <v>1</v>
@@ -19324,8 +19296,8 @@
       <c r="A51" s="13">
         <v>2</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>14</v>
+      <c r="B51" s="16">
+        <v>1</v>
       </c>
       <c r="C51" s="13">
         <v>1</v>
@@ -19335,8 +19307,8 @@
       <c r="A52" s="12">
         <v>1</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>14</v>
+      <c r="B52" s="15">
+        <v>1</v>
       </c>
       <c r="C52" s="12">
         <v>1</v>
@@ -19346,8 +19318,8 @@
       <c r="A53" s="13">
         <v>3</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>14</v>
+      <c r="B53" s="16">
+        <v>1</v>
       </c>
       <c r="C53" s="13">
         <v>1</v>
@@ -19357,8 +19329,8 @@
       <c r="A54" s="12">
         <v>2</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>14</v>
+      <c r="B54" s="15">
+        <v>1</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
@@ -19368,8 +19340,8 @@
       <c r="A55" s="13">
         <v>2</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>14</v>
+      <c r="B55" s="16">
+        <v>1</v>
       </c>
       <c r="C55" s="13">
         <v>2</v>
@@ -19379,8 +19351,8 @@
       <c r="A56" s="12">
         <v>2</v>
       </c>
-      <c r="B56" s="15" t="s">
-        <v>15</v>
+      <c r="B56" s="15">
+        <v>2</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
@@ -19390,8 +19362,8 @@
       <c r="A57" s="13">
         <v>2</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>14</v>
+      <c r="B57" s="16">
+        <v>1</v>
       </c>
       <c r="C57" s="13">
         <v>2</v>
@@ -19401,8 +19373,8 @@
       <c r="A58" s="12">
         <v>2</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>14</v>
+      <c r="B58" s="15">
+        <v>1</v>
       </c>
       <c r="C58" s="12">
         <v>1</v>
@@ -19412,8 +19384,8 @@
       <c r="A59" s="13">
         <v>2</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>14</v>
+      <c r="B59" s="16">
+        <v>1</v>
       </c>
       <c r="C59" s="13">
         <v>1</v>
@@ -19423,8 +19395,8 @@
       <c r="A60" s="12">
         <v>1</v>
       </c>
-      <c r="B60" s="15" t="s">
-        <v>14</v>
+      <c r="B60" s="15">
+        <v>1</v>
       </c>
       <c r="C60" s="12">
         <v>2</v>
@@ -19434,8 +19406,8 @@
       <c r="A61" s="13">
         <v>2</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>15</v>
+      <c r="B61" s="16">
+        <v>2</v>
       </c>
       <c r="C61" s="13">
         <v>0</v>
@@ -19445,8 +19417,8 @@
       <c r="A62" s="12">
         <v>3</v>
       </c>
-      <c r="B62" s="15" t="s">
-        <v>14</v>
+      <c r="B62" s="15">
+        <v>1</v>
       </c>
       <c r="C62" s="12">
         <v>1</v>
@@ -19456,8 +19428,8 @@
       <c r="A63" s="13">
         <v>2</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>14</v>
+      <c r="B63" s="16">
+        <v>1</v>
       </c>
       <c r="C63" s="13">
         <v>1</v>
@@ -19467,8 +19439,8 @@
       <c r="A64" s="12">
         <v>3</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>14</v>
+      <c r="B64" s="15">
+        <v>1</v>
       </c>
       <c r="C64" s="12">
         <v>1</v>
@@ -19478,8 +19450,8 @@
       <c r="A65" s="13">
         <v>1</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>14</v>
+      <c r="B65" s="16">
+        <v>1</v>
       </c>
       <c r="C65" s="13">
         <v>2</v>
@@ -19489,8 +19461,8 @@
       <c r="A66" s="12">
         <v>1</v>
       </c>
-      <c r="B66" s="15" t="s">
-        <v>14</v>
+      <c r="B66" s="15">
+        <v>1</v>
       </c>
       <c r="C66" s="12">
         <v>1</v>
@@ -19500,8 +19472,8 @@
       <c r="A67" s="13">
         <v>3</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>14</v>
+      <c r="B67" s="16">
+        <v>1</v>
       </c>
       <c r="C67" s="13">
         <v>1</v>
@@ -19511,8 +19483,8 @@
       <c r="A68" s="12">
         <v>2</v>
       </c>
-      <c r="B68" s="15" t="s">
-        <v>14</v>
+      <c r="B68" s="15">
+        <v>1</v>
       </c>
       <c r="C68" s="12">
         <v>1</v>
@@ -19522,8 +19494,8 @@
       <c r="A69" s="13">
         <v>3</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>15</v>
+      <c r="B69" s="16">
+        <v>2</v>
       </c>
       <c r="C69" s="13">
         <v>0</v>
@@ -19533,8 +19505,8 @@
       <c r="A70" s="12">
         <v>2</v>
       </c>
-      <c r="B70" s="15" t="s">
-        <v>14</v>
+      <c r="B70" s="15">
+        <v>1</v>
       </c>
       <c r="C70" s="12">
         <v>1</v>
@@ -19544,8 +19516,8 @@
       <c r="A71" s="13">
         <v>2</v>
       </c>
-      <c r="B71" s="16" t="s">
-        <v>14</v>
+      <c r="B71" s="16">
+        <v>1</v>
       </c>
       <c r="C71" s="13">
         <v>1</v>
@@ -19555,8 +19527,8 @@
       <c r="A72" s="12">
         <v>2</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>15</v>
+      <c r="B72" s="15">
+        <v>2</v>
       </c>
       <c r="C72" s="12">
         <v>0</v>
@@ -19566,8 +19538,8 @@
       <c r="A73" s="13">
         <v>2</v>
       </c>
-      <c r="B73" s="16" t="s">
-        <v>14</v>
+      <c r="B73" s="16">
+        <v>1</v>
       </c>
       <c r="C73" s="13">
         <v>1</v>
@@ -19577,8 +19549,8 @@
       <c r="A74" s="12">
         <v>2</v>
       </c>
-      <c r="B74" s="15" t="s">
-        <v>14</v>
+      <c r="B74" s="15">
+        <v>1</v>
       </c>
       <c r="C74" s="12">
         <v>1</v>
@@ -19588,8 +19560,8 @@
       <c r="A75" s="13">
         <v>2</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>15</v>
+      <c r="B75" s="16">
+        <v>2</v>
       </c>
       <c r="C75" s="13">
         <v>1</v>
@@ -19599,8 +19571,8 @@
       <c r="A76" s="12">
         <v>1</v>
       </c>
-      <c r="B76" s="15" t="s">
-        <v>15</v>
+      <c r="B76" s="15">
+        <v>2</v>
       </c>
       <c r="C76" s="12">
         <v>1</v>
@@ -19610,8 +19582,8 @@
       <c r="A77" s="13">
         <v>1</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>15</v>
+      <c r="B77" s="16">
+        <v>2</v>
       </c>
       <c r="C77" s="13">
         <v>0</v>
@@ -19621,8 +19593,8 @@
       <c r="A78" s="12">
         <v>4</v>
       </c>
-      <c r="B78" s="15" t="s">
-        <v>14</v>
+      <c r="B78" s="15">
+        <v>1</v>
       </c>
       <c r="C78" s="12">
         <v>1</v>
@@ -19632,8 +19604,8 @@
       <c r="A79" s="13">
         <v>1</v>
       </c>
-      <c r="B79" s="16" t="s">
-        <v>15</v>
+      <c r="B79" s="16">
+        <v>2</v>
       </c>
       <c r="C79" s="13">
         <v>1</v>
@@ -19643,8 +19615,8 @@
       <c r="A80" s="12">
         <v>3</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>14</v>
+      <c r="B80" s="15">
+        <v>1</v>
       </c>
       <c r="C80" s="12">
         <v>1</v>
@@ -19654,8 +19626,8 @@
       <c r="A81" s="13">
         <v>2</v>
       </c>
-      <c r="B81" s="16" t="s">
-        <v>14</v>
+      <c r="B81" s="16">
+        <v>1</v>
       </c>
       <c r="C81" s="13">
         <v>1</v>
@@ -19665,8 +19637,8 @@
       <c r="A82" s="12">
         <v>3</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>14</v>
+      <c r="B82" s="15">
+        <v>1</v>
       </c>
       <c r="C82" s="12">
         <v>1</v>
@@ -19676,8 +19648,8 @@
       <c r="A83" s="13">
         <v>3</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>15</v>
+      <c r="B83" s="16">
+        <v>2</v>
       </c>
       <c r="C83" s="13">
         <v>1</v>
@@ -19687,8 +19659,8 @@
       <c r="A84" s="12">
         <v>2</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>14</v>
+      <c r="B84" s="15">
+        <v>1</v>
       </c>
       <c r="C84" s="12">
         <v>2</v>
@@ -19698,8 +19670,8 @@
       <c r="A85" s="13">
         <v>2</v>
       </c>
-      <c r="B85" s="16" t="s">
-        <v>15</v>
+      <c r="B85" s="16">
+        <v>2</v>
       </c>
       <c r="C85" s="13">
         <v>0</v>
@@ -19709,8 +19681,8 @@
       <c r="A86" s="12">
         <v>1</v>
       </c>
-      <c r="B86" s="15" t="s">
-        <v>14</v>
+      <c r="B86" s="15">
+        <v>1</v>
       </c>
       <c r="C86" s="12">
         <v>1</v>
@@ -19720,8 +19692,8 @@
       <c r="A87" s="13">
         <v>2</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>14</v>
+      <c r="B87" s="16">
+        <v>1</v>
       </c>
       <c r="C87" s="13">
         <v>1</v>
@@ -19731,8 +19703,8 @@
       <c r="A88" s="12">
         <v>2</v>
       </c>
-      <c r="B88" s="15" t="s">
-        <v>14</v>
+      <c r="B88" s="15">
+        <v>1</v>
       </c>
       <c r="C88" s="12">
         <v>1</v>
@@ -19742,8 +19714,8 @@
       <c r="A89" s="13">
         <v>3</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>14</v>
+      <c r="B89" s="16">
+        <v>1</v>
       </c>
       <c r="C89" s="13">
         <v>1</v>
@@ -19753,8 +19725,8 @@
       <c r="A90" s="12">
         <v>2</v>
       </c>
-      <c r="B90" s="15" t="s">
-        <v>14</v>
+      <c r="B90" s="15">
+        <v>1</v>
       </c>
       <c r="C90" s="12">
         <v>1</v>
@@ -19764,8 +19736,8 @@
       <c r="A91" s="13">
         <v>2</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>14</v>
+      <c r="B91" s="16">
+        <v>1</v>
       </c>
       <c r="C91" s="13">
         <v>1</v>
@@ -19775,8 +19747,8 @@
       <c r="A92" s="12">
         <v>1</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>14</v>
+      <c r="B92" s="15">
+        <v>1</v>
       </c>
       <c r="C92" s="12">
         <v>1</v>
@@ -19786,8 +19758,8 @@
       <c r="A93" s="13">
         <v>2</v>
       </c>
-      <c r="B93" s="16" t="s">
-        <v>14</v>
+      <c r="B93" s="16">
+        <v>1</v>
       </c>
       <c r="C93" s="13">
         <v>2</v>
@@ -19797,8 +19769,8 @@
       <c r="A94" s="12">
         <v>2</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>14</v>
+      <c r="B94" s="15">
+        <v>1</v>
       </c>
       <c r="C94" s="12">
         <v>0</v>
@@ -19808,8 +19780,8 @@
       <c r="A95" s="13">
         <v>2</v>
       </c>
-      <c r="B95" s="16" t="s">
-        <v>14</v>
+      <c r="B95" s="16">
+        <v>1</v>
       </c>
       <c r="C95" s="13">
         <v>1</v>
@@ -19819,8 +19791,8 @@
       <c r="A96" s="12">
         <v>3</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>14</v>
+      <c r="B96" s="15">
+        <v>1</v>
       </c>
       <c r="C96" s="12">
         <v>1</v>
@@ -19830,8 +19802,8 @@
       <c r="A97" s="13">
         <v>1</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>14</v>
+      <c r="B97" s="16">
+        <v>1</v>
       </c>
       <c r="C97" s="13">
         <v>0</v>
@@ -19841,8 +19813,8 @@
       <c r="A98" s="12">
         <v>1</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>15</v>
+      <c r="B98" s="15">
+        <v>2</v>
       </c>
       <c r="C98" s="12">
         <v>1</v>
@@ -19852,8 +19824,8 @@
       <c r="A99" s="13">
         <v>1</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>15</v>
+      <c r="B99" s="16">
+        <v>2</v>
       </c>
       <c r="C99" s="13">
         <v>0</v>
@@ -19863,8 +19835,8 @@
       <c r="A100" s="12">
         <v>3</v>
       </c>
-      <c r="B100" s="15" t="s">
-        <v>14</v>
+      <c r="B100" s="15">
+        <v>1</v>
       </c>
       <c r="C100" s="12">
         <v>1</v>
@@ -19874,8 +19846,8 @@
       <c r="A101" s="13">
         <v>3</v>
       </c>
-      <c r="B101" s="16" t="s">
-        <v>14</v>
+      <c r="B101" s="16">
+        <v>1</v>
       </c>
       <c r="C101" s="13">
         <v>1</v>
@@ -19885,8 +19857,8 @@
       <c r="A102" s="12">
         <v>2</v>
       </c>
-      <c r="B102" s="15" t="s">
-        <v>14</v>
+      <c r="B102" s="15">
+        <v>1</v>
       </c>
       <c r="C102" s="12">
         <v>0</v>
@@ -19896,8 +19868,8 @@
       <c r="A103" s="13">
         <v>3</v>
       </c>
-      <c r="B103" s="16" t="s">
-        <v>15</v>
+      <c r="B103" s="16">
+        <v>2</v>
       </c>
       <c r="C103" s="13">
         <v>1</v>
@@ -19907,8 +19879,8 @@
       <c r="A104" s="12">
         <v>2</v>
       </c>
-      <c r="B104" s="15" t="s">
-        <v>14</v>
+      <c r="B104" s="15">
+        <v>1</v>
       </c>
       <c r="C104" s="12">
         <v>1</v>
@@ -19918,8 +19890,8 @@
       <c r="A105" s="13">
         <v>1</v>
       </c>
-      <c r="B105" s="16" t="s">
-        <v>15</v>
+      <c r="B105" s="16">
+        <v>2</v>
       </c>
       <c r="C105" s="13">
         <v>0</v>
@@ -19929,8 +19901,8 @@
       <c r="A106" s="12">
         <v>1</v>
       </c>
-      <c r="B106" s="15" t="s">
-        <v>14</v>
+      <c r="B106" s="15">
+        <v>1</v>
       </c>
       <c r="C106" s="12">
         <v>0</v>
@@ -19940,8 +19912,8 @@
       <c r="A107" s="13">
         <v>2</v>
       </c>
-      <c r="B107" s="16" t="s">
-        <v>14</v>
+      <c r="B107" s="16">
+        <v>1</v>
       </c>
       <c r="C107" s="13">
         <v>14</v>
@@ -19951,8 +19923,8 @@
       <c r="A108" s="12">
         <v>1</v>
       </c>
-      <c r="B108" s="15" t="s">
-        <v>14</v>
+      <c r="B108" s="15">
+        <v>1</v>
       </c>
       <c r="C108" s="12">
         <v>1</v>
@@ -19962,8 +19934,8 @@
       <c r="A109" s="13">
         <v>2</v>
       </c>
-      <c r="B109" s="16" t="s">
-        <v>14</v>
+      <c r="B109" s="16">
+        <v>1</v>
       </c>
       <c r="C109" s="13">
         <v>0</v>
@@ -19973,8 +19945,8 @@
       <c r="A110" s="12">
         <v>2</v>
       </c>
-      <c r="B110" s="15" t="s">
-        <v>14</v>
+      <c r="B110" s="15">
+        <v>1</v>
       </c>
       <c r="C110" s="12">
         <v>1</v>
@@ -19984,8 +19956,8 @@
       <c r="A111" s="13">
         <v>2</v>
       </c>
-      <c r="B111" s="16" t="s">
-        <v>15</v>
+      <c r="B111" s="16">
+        <v>2</v>
       </c>
       <c r="C111" s="13">
         <v>0</v>
@@ -19995,8 +19967,8 @@
       <c r="A112" s="12">
         <v>3</v>
       </c>
-      <c r="B112" s="15" t="s">
-        <v>14</v>
+      <c r="B112" s="15">
+        <v>1</v>
       </c>
       <c r="C112" s="12">
         <v>1</v>
@@ -20006,8 +19978,8 @@
       <c r="A113" s="13">
         <v>1</v>
       </c>
-      <c r="B113" s="16" t="s">
-        <v>14</v>
+      <c r="B113" s="16">
+        <v>1</v>
       </c>
       <c r="C113" s="13">
         <v>1</v>
@@ -20017,8 +19989,8 @@
       <c r="A114" s="12">
         <v>1</v>
       </c>
-      <c r="B114" s="15" t="s">
-        <v>15</v>
+      <c r="B114" s="15">
+        <v>2</v>
       </c>
       <c r="C114" s="12">
         <v>2</v>
@@ -20028,8 +20000,8 @@
       <c r="A115" s="13">
         <v>1</v>
       </c>
-      <c r="B115" s="16" t="s">
-        <v>14</v>
+      <c r="B115" s="16">
+        <v>1</v>
       </c>
       <c r="C115" s="13">
         <v>1</v>
@@ -20039,8 +20011,8 @@
       <c r="A116" s="12">
         <v>1</v>
       </c>
-      <c r="B116" s="15" t="s">
-        <v>15</v>
+      <c r="B116" s="15">
+        <v>2</v>
       </c>
       <c r="C116" s="12">
         <v>1</v>
@@ -20050,8 +20022,8 @@
       <c r="A117" s="13">
         <v>1</v>
       </c>
-      <c r="B117" s="16" t="s">
-        <v>15</v>
+      <c r="B117" s="16">
+        <v>2</v>
       </c>
       <c r="C117" s="13">
         <v>0</v>
@@ -20061,8 +20033,8 @@
       <c r="A118" s="12">
         <v>1</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>14</v>
+      <c r="B118" s="15">
+        <v>1</v>
       </c>
       <c r="C118" s="12">
         <v>2</v>
@@ -20072,8 +20044,8 @@
       <c r="A119" s="13">
         <v>2</v>
       </c>
-      <c r="B119" s="16" t="s">
-        <v>14</v>
+      <c r="B119" s="16">
+        <v>1</v>
       </c>
       <c r="C119" s="13">
         <v>1</v>
@@ -20083,8 +20055,8 @@
       <c r="A120" s="12">
         <v>2</v>
       </c>
-      <c r="B120" s="15" t="s">
-        <v>14</v>
+      <c r="B120" s="15">
+        <v>1</v>
       </c>
       <c r="C120" s="12">
         <v>2</v>
@@ -20094,8 +20066,8 @@
       <c r="A121" s="13">
         <v>2</v>
       </c>
-      <c r="B121" s="16" t="s">
-        <v>14</v>
+      <c r="B121" s="16">
+        <v>1</v>
       </c>
       <c r="C121" s="13">
         <v>2</v>
@@ -20105,8 +20077,8 @@
       <c r="A122" s="12">
         <v>2</v>
       </c>
-      <c r="B122" s="15" t="s">
-        <v>14</v>
+      <c r="B122" s="15">
+        <v>1</v>
       </c>
       <c r="C122" s="12">
         <v>1</v>
@@ -20116,8 +20088,8 @@
       <c r="A123" s="13">
         <v>1</v>
       </c>
-      <c r="B123" s="16" t="s">
-        <v>14</v>
+      <c r="B123" s="16">
+        <v>1</v>
       </c>
       <c r="C123" s="13">
         <v>2</v>
@@ -20127,8 +20099,8 @@
       <c r="A124" s="12">
         <v>3</v>
       </c>
-      <c r="B124" s="15" t="s">
-        <v>15</v>
+      <c r="B124" s="15">
+        <v>2</v>
       </c>
       <c r="C124" s="12">
         <v>0</v>
@@ -20138,8 +20110,8 @@
       <c r="A125" s="13">
         <v>2</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>14</v>
+      <c r="B125" s="16">
+        <v>1</v>
       </c>
       <c r="C125" s="13">
         <v>2</v>
@@ -20149,8 +20121,8 @@
       <c r="A126" s="12">
         <v>2</v>
       </c>
-      <c r="B126" s="15" t="s">
-        <v>14</v>
+      <c r="B126" s="15">
+        <v>1</v>
       </c>
       <c r="C126" s="12">
         <v>1</v>
@@ -20160,8 +20132,8 @@
       <c r="A127" s="13">
         <v>1</v>
       </c>
-      <c r="B127" s="16" t="s">
-        <v>14</v>
+      <c r="B127" s="16">
+        <v>1</v>
       </c>
       <c r="C127" s="13">
         <v>2</v>
@@ -20171,8 +20143,8 @@
       <c r="A128" s="12">
         <v>2</v>
       </c>
-      <c r="B128" s="15" t="s">
-        <v>15</v>
+      <c r="B128" s="15">
+        <v>2</v>
       </c>
       <c r="C128" s="12">
         <v>1</v>
@@ -20182,8 +20154,8 @@
       <c r="A129" s="13">
         <v>2</v>
       </c>
-      <c r="B129" s="16" t="s">
-        <v>14</v>
+      <c r="B129" s="16">
+        <v>1</v>
       </c>
       <c r="C129" s="13">
         <v>1</v>
@@ -20193,8 +20165,8 @@
       <c r="A130" s="12">
         <v>2</v>
       </c>
-      <c r="B130" s="15" t="s">
-        <v>14</v>
+      <c r="B130" s="15">
+        <v>1</v>
       </c>
       <c r="C130" s="12">
         <v>1</v>
@@ -20204,8 +20176,8 @@
       <c r="A131" s="13">
         <v>3</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>14</v>
+      <c r="B131" s="16">
+        <v>1</v>
       </c>
       <c r="C131" s="13">
         <v>2</v>
@@ -20215,8 +20187,8 @@
       <c r="A132" s="12">
         <v>3</v>
       </c>
-      <c r="B132" s="15" t="s">
-        <v>14</v>
+      <c r="B132" s="15">
+        <v>1</v>
       </c>
       <c r="C132" s="12">
         <v>2</v>
@@ -20226,8 +20198,8 @@
       <c r="A133" s="13">
         <v>2</v>
       </c>
-      <c r="B133" s="16" t="s">
-        <v>14</v>
+      <c r="B133" s="16">
+        <v>1</v>
       </c>
       <c r="C133" s="13">
         <v>1</v>
@@ -20237,8 +20209,8 @@
       <c r="A134" s="12">
         <v>1</v>
       </c>
-      <c r="B134" s="15" t="s">
-        <v>14</v>
+      <c r="B134" s="15">
+        <v>1</v>
       </c>
       <c r="C134" s="12">
         <v>1</v>
@@ -20248,8 +20220,8 @@
       <c r="A135" s="13">
         <v>2</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>14</v>
+      <c r="B135" s="16">
+        <v>1</v>
       </c>
       <c r="C135" s="13">
         <v>1</v>
@@ -20259,3768 +20231,3757 @@
       <c r="A136" s="14">
         <v>2</v>
       </c>
-      <c r="B136" s="18" t="s">
+      <c r="B136" s="18">
+        <v>2</v>
+      </c>
+      <c r="C136" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="12">
+        <v>1</v>
+      </c>
+      <c r="B137" s="15">
+        <v>2</v>
+      </c>
+      <c r="C137" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="13">
+        <v>2</v>
+      </c>
+      <c r="B138" s="16">
+        <v>2</v>
+      </c>
+      <c r="C138" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="12">
+        <v>2</v>
+      </c>
+      <c r="B139" s="15">
+        <v>1</v>
+      </c>
+      <c r="C139" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="13">
+        <v>3</v>
+      </c>
+      <c r="B140" s="16">
+        <v>2</v>
+      </c>
+      <c r="C140" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="12">
+        <v>3</v>
+      </c>
+      <c r="B141" s="15">
+        <v>2</v>
+      </c>
+      <c r="C141" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="13">
+        <v>1</v>
+      </c>
+      <c r="B142" s="16">
+        <v>1</v>
+      </c>
+      <c r="C142" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="12">
+        <v>1</v>
+      </c>
+      <c r="B143" s="15">
+        <v>2</v>
+      </c>
+      <c r="C143" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="13">
+        <v>2</v>
+      </c>
+      <c r="B144" s="16">
+        <v>1</v>
+      </c>
+      <c r="C144" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="12">
+        <v>2</v>
+      </c>
+      <c r="B145" s="15">
+        <v>2</v>
+      </c>
+      <c r="C145" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="13">
+        <v>2</v>
+      </c>
+      <c r="B146" s="16">
+        <v>2</v>
+      </c>
+      <c r="C146" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="12">
+        <v>3</v>
+      </c>
+      <c r="B147" s="15">
+        <v>1</v>
+      </c>
+      <c r="C147" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="13">
+        <v>2</v>
+      </c>
+      <c r="B148" s="16">
+        <v>2</v>
+      </c>
+      <c r="C148" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="12">
+        <v>1</v>
+      </c>
+      <c r="B149" s="15">
+        <v>1</v>
+      </c>
+      <c r="C149" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="13">
+        <v>2</v>
+      </c>
+      <c r="B150" s="16">
+        <v>1</v>
+      </c>
+      <c r="C150" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="12">
+        <v>2</v>
+      </c>
+      <c r="B151" s="15">
+        <v>1</v>
+      </c>
+      <c r="C151" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="13">
+        <v>2</v>
+      </c>
+      <c r="B152" s="16">
+        <v>2</v>
+      </c>
+      <c r="C152" s="17"/>
+    </row>
+    <row r="153" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A153" s="12">
+        <v>3</v>
+      </c>
+      <c r="B153" s="15">
+        <v>1</v>
+      </c>
+      <c r="C153" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="13">
+        <v>1</v>
+      </c>
+      <c r="B154" s="16">
+        <v>1</v>
+      </c>
+      <c r="C154" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="12">
+        <v>2</v>
+      </c>
+      <c r="B155" s="15">
+        <v>1</v>
+      </c>
+      <c r="C155" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="13">
+        <v>3</v>
+      </c>
+      <c r="B156" s="16">
+        <v>1</v>
+      </c>
+      <c r="C156" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="12">
+        <v>3</v>
+      </c>
+      <c r="B157" s="15">
+        <v>1</v>
+      </c>
+      <c r="C157" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="13">
+        <v>3</v>
+      </c>
+      <c r="B158" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C158" s="17"/>
+    </row>
+    <row r="159" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="12">
+        <v>2</v>
+      </c>
+      <c r="B159" s="15">
+        <v>1</v>
+      </c>
+      <c r="C159" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="13">
+        <v>1</v>
+      </c>
+      <c r="B160" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="12">
+        <v>1</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C161" s="19"/>
+    </row>
+    <row r="162" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="13">
+        <v>2</v>
+      </c>
+      <c r="B162" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" s="17"/>
+    </row>
+    <row r="163" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A163" s="12">
+        <v>1</v>
+      </c>
+      <c r="B163" s="15">
+        <v>1</v>
+      </c>
+      <c r="C163" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="13">
+        <v>2</v>
+      </c>
+      <c r="B164" s="16">
+        <v>1</v>
+      </c>
+      <c r="C164" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="12">
+        <v>3</v>
+      </c>
+      <c r="B165" s="15">
+        <v>1</v>
+      </c>
+      <c r="C165" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="13">
+        <v>3</v>
+      </c>
+      <c r="B166" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C166" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="12">
+        <v>1</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C167" s="19"/>
+    </row>
+    <row r="168" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="13">
+        <v>1</v>
+      </c>
+      <c r="B168" s="16">
+        <v>2</v>
+      </c>
+      <c r="C168" s="17"/>
+    </row>
+    <row r="169" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="12">
+        <v>2</v>
+      </c>
+      <c r="B169" s="15">
+        <v>1</v>
+      </c>
+      <c r="C169" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="13">
+        <v>3</v>
+      </c>
+      <c r="B170" s="16">
+        <v>1</v>
+      </c>
+      <c r="C170" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="12">
+        <v>2</v>
+      </c>
+      <c r="B171" s="15">
+        <v>1</v>
+      </c>
+      <c r="C171" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="13">
+        <v>1</v>
+      </c>
+      <c r="B172" s="16">
+        <v>1</v>
+      </c>
+      <c r="C172" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="12">
+        <v>1</v>
+      </c>
+      <c r="B173" s="15">
+        <v>1</v>
+      </c>
+      <c r="C173" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="13">
+        <v>2</v>
+      </c>
+      <c r="B174" s="16">
+        <v>2</v>
+      </c>
+      <c r="C174" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="12">
+        <v>2</v>
+      </c>
+      <c r="B175" s="15">
+        <v>1</v>
+      </c>
+      <c r="C175" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="13">
+        <v>2</v>
+      </c>
+      <c r="B176" s="16">
+        <v>1</v>
+      </c>
+      <c r="C176" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="12">
+        <v>2</v>
+      </c>
+      <c r="B177" s="15">
+        <v>1</v>
+      </c>
+      <c r="C177" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="13">
+        <v>3</v>
+      </c>
+      <c r="B178" s="16">
+        <v>1</v>
+      </c>
+      <c r="C178" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="12">
+        <v>2</v>
+      </c>
+      <c r="B179" s="15">
+        <v>1</v>
+      </c>
+      <c r="C179" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="13">
+        <v>2</v>
+      </c>
+      <c r="B180" s="16">
+        <v>1</v>
+      </c>
+      <c r="C180" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="12">
+        <v>2</v>
+      </c>
+      <c r="B181" s="15">
+        <v>1</v>
+      </c>
+      <c r="C181" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A182" s="13">
+        <v>1</v>
+      </c>
+      <c r="B182" s="16">
+        <v>2</v>
+      </c>
+      <c r="C182" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A183" s="12">
+        <v>1</v>
+      </c>
+      <c r="B183" s="15">
+        <v>2</v>
+      </c>
+      <c r="C183" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A184" s="13">
+        <v>2</v>
+      </c>
+      <c r="B184" s="16">
+        <v>1</v>
+      </c>
+      <c r="C184" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="12">
+        <v>3</v>
+      </c>
+      <c r="B185" s="15">
+        <v>1</v>
+      </c>
+      <c r="C185" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="13">
+        <v>2</v>
+      </c>
+      <c r="B186" s="16">
+        <v>1</v>
+      </c>
+      <c r="C186" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="12">
+        <v>1</v>
+      </c>
+      <c r="B187" s="15">
+        <v>1</v>
+      </c>
+      <c r="C187" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A188" s="13">
+        <v>2</v>
+      </c>
+      <c r="B188" s="16">
+        <v>1</v>
+      </c>
+      <c r="C188" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A189" s="12">
+        <v>3</v>
+      </c>
+      <c r="B189" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A190" s="13">
+        <v>3</v>
+      </c>
+      <c r="B190" s="16">
+        <v>2</v>
+      </c>
+      <c r="C190" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A191" s="12">
+        <v>3</v>
+      </c>
+      <c r="B191" s="15">
+        <v>1</v>
+      </c>
+      <c r="C191" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A192" s="13">
+        <v>3</v>
+      </c>
+      <c r="B192" s="16">
+        <v>1</v>
+      </c>
+      <c r="C192" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A193" s="12">
+        <v>2</v>
+      </c>
+      <c r="B193" s="15">
+        <v>1</v>
+      </c>
+      <c r="C193" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A194" s="13">
+        <v>3</v>
+      </c>
+      <c r="B194" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C194" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A195" s="12">
+        <v>2</v>
+      </c>
+      <c r="B195" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C195" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="13">
+        <v>2</v>
+      </c>
+      <c r="B196" s="16">
+        <v>1</v>
+      </c>
+      <c r="C196" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="12">
+        <v>2</v>
+      </c>
+      <c r="B197" s="15">
+        <v>1</v>
+      </c>
+      <c r="C197" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="13">
+        <v>1</v>
+      </c>
+      <c r="B198" s="16">
+        <v>1</v>
+      </c>
+      <c r="C198" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="12">
+        <v>2</v>
+      </c>
+      <c r="B199" s="15">
+        <v>1</v>
+      </c>
+      <c r="C199" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="13">
+        <v>2</v>
+      </c>
+      <c r="B200" s="16">
+        <v>1</v>
+      </c>
+      <c r="C200" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="12">
+        <v>2</v>
+      </c>
+      <c r="B201" s="15">
+        <v>1</v>
+      </c>
+      <c r="C201" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="13">
+        <v>2</v>
+      </c>
+      <c r="B202" s="16">
+        <v>1</v>
+      </c>
+      <c r="C202" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A203" s="12">
+        <v>1</v>
+      </c>
+      <c r="B203" s="15">
+        <v>1</v>
+      </c>
+      <c r="C203" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="13">
+        <v>2</v>
+      </c>
+      <c r="B204" s="16">
+        <v>1</v>
+      </c>
+      <c r="C204" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="12">
+        <v>3</v>
+      </c>
+      <c r="B205" s="15">
+        <v>2</v>
+      </c>
+      <c r="C205" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A206" s="13">
+        <v>2</v>
+      </c>
+      <c r="B206" s="16">
+        <v>1</v>
+      </c>
+      <c r="C206" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="12">
+        <v>2</v>
+      </c>
+      <c r="B207" s="15">
+        <v>1</v>
+      </c>
+      <c r="C207" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="13">
+        <v>3</v>
+      </c>
+      <c r="B208" s="16">
+        <v>1</v>
+      </c>
+      <c r="C208" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A209" s="12">
+        <v>3</v>
+      </c>
+      <c r="B209" s="15">
+        <v>1</v>
+      </c>
+      <c r="C209" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="13">
+        <v>1</v>
+      </c>
+      <c r="B210" s="16">
+        <v>1</v>
+      </c>
+      <c r="C210" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="12">
+        <v>2</v>
+      </c>
+      <c r="B211" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C136" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="221.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="11" t="s">
+      <c r="C211" s="19"/>
+    </row>
+    <row r="212" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="13">
+        <v>2</v>
+      </c>
+      <c r="B212" s="16">
+        <v>1</v>
+      </c>
+      <c r="C212" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A213" s="12">
+        <v>1</v>
+      </c>
+      <c r="B213" s="15">
+        <v>1</v>
+      </c>
+      <c r="C213" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="13">
+        <v>1</v>
+      </c>
+      <c r="B214" s="16">
+        <v>1</v>
+      </c>
+      <c r="C214" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="12">
+        <v>2</v>
+      </c>
+      <c r="B215" s="15">
+        <v>1</v>
+      </c>
+      <c r="C215" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="13">
+        <v>2</v>
+      </c>
+      <c r="B216" s="16">
+        <v>1</v>
+      </c>
+      <c r="C216" s="13">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="12">
+        <v>2</v>
+      </c>
+      <c r="B217" s="15">
+        <v>1</v>
+      </c>
+      <c r="C217" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A218" s="13">
+        <v>2</v>
+      </c>
+      <c r="B218" s="16">
+        <v>1</v>
+      </c>
+      <c r="C218" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A219" s="12">
+        <v>2</v>
+      </c>
+      <c r="B219" s="15">
+        <v>1</v>
+      </c>
+      <c r="C219" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="13">
+        <v>2</v>
+      </c>
+      <c r="B220" s="16">
+        <v>1</v>
+      </c>
+      <c r="C220" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="12">
+        <v>2</v>
+      </c>
+      <c r="B221" s="15">
+        <v>1</v>
+      </c>
+      <c r="C221" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="13">
+        <v>2</v>
+      </c>
+      <c r="B222" s="16">
+        <v>1</v>
+      </c>
+      <c r="C222" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="12">
+        <v>2</v>
+      </c>
+      <c r="B223" s="15">
+        <v>1</v>
+      </c>
+      <c r="C223" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="13">
+        <v>1</v>
+      </c>
+      <c r="B224" s="16">
+        <v>1</v>
+      </c>
+      <c r="C224" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="12">
+        <v>2</v>
+      </c>
+      <c r="B225" s="15">
+        <v>1</v>
+      </c>
+      <c r="C225" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="13">
+        <v>2</v>
+      </c>
+      <c r="B226" s="16">
+        <v>2</v>
+      </c>
+      <c r="C226" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227" s="12">
+        <v>3</v>
+      </c>
+      <c r="B227" s="15">
+        <v>1</v>
+      </c>
+      <c r="C227" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A228" s="13">
+        <v>1</v>
+      </c>
+      <c r="B228" s="16">
+        <v>1</v>
+      </c>
+      <c r="C228" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="12">
+        <v>2</v>
+      </c>
+      <c r="B229" s="15">
+        <v>1</v>
+      </c>
+      <c r="C229" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="13">
+        <v>3</v>
+      </c>
+      <c r="B230" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C230" s="17"/>
+    </row>
+    <row r="231" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231" s="12">
+        <v>2</v>
+      </c>
+      <c r="B231" s="15">
+        <v>1</v>
+      </c>
+      <c r="C231" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="13">
+        <v>1</v>
+      </c>
+      <c r="B232" s="16">
+        <v>1</v>
+      </c>
+      <c r="C232" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A233" s="12">
+        <v>1</v>
+      </c>
+      <c r="B233" s="15">
+        <v>1</v>
+      </c>
+      <c r="C233" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A234" s="13">
+        <v>2</v>
+      </c>
+      <c r="B234" s="16">
+        <v>1</v>
+      </c>
+      <c r="C234" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A235" s="12">
+        <v>1</v>
+      </c>
+      <c r="B235" s="15">
+        <v>1</v>
+      </c>
+      <c r="C235" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="13">
+        <v>1</v>
+      </c>
+      <c r="B236" s="16">
+        <v>1</v>
+      </c>
+      <c r="C236" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A237" s="12">
+        <v>1</v>
+      </c>
+      <c r="B237" s="15">
+        <v>1</v>
+      </c>
+      <c r="C237" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A238" s="13">
+        <v>2</v>
+      </c>
+      <c r="B238" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C238" s="17"/>
+    </row>
+    <row r="239" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A239" s="12">
+        <v>1</v>
+      </c>
+      <c r="B239" s="15">
+        <v>1</v>
+      </c>
+      <c r="C239" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A240" s="13">
+        <v>2</v>
+      </c>
+      <c r="B240" s="16">
+        <v>1</v>
+      </c>
+      <c r="C240" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A241" s="12">
+        <v>2</v>
+      </c>
+      <c r="B241" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C241" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A242" s="13">
+        <v>1</v>
+      </c>
+      <c r="B242" s="16">
+        <v>1</v>
+      </c>
+      <c r="C242" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A243" s="12">
+        <v>1</v>
+      </c>
+      <c r="B243" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C243" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A244" s="13">
+        <v>1</v>
+      </c>
+      <c r="B244" s="16">
+        <v>1</v>
+      </c>
+      <c r="C244" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="12">
+        <v>2</v>
+      </c>
+      <c r="B245" s="15">
+        <v>1</v>
+      </c>
+      <c r="C245" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A246" s="13">
+        <v>1</v>
+      </c>
+      <c r="B246" s="16">
+        <v>1</v>
+      </c>
+      <c r="C246" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A247" s="12">
+        <v>1</v>
+      </c>
+      <c r="B247" s="15">
+        <v>1</v>
+      </c>
+      <c r="C247" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A248" s="13">
+        <v>4</v>
+      </c>
+      <c r="B248" s="16">
+        <v>1</v>
+      </c>
+      <c r="C248" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A249" s="12">
+        <v>2</v>
+      </c>
+      <c r="B249" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A250" s="13">
+        <v>2</v>
+      </c>
+      <c r="B250" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C250" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A251" s="12">
+        <v>2</v>
+      </c>
+      <c r="B251" s="15">
+        <v>1</v>
+      </c>
+      <c r="C251" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="13">
+        <v>1</v>
+      </c>
+      <c r="B252" s="16">
+        <v>1</v>
+      </c>
+      <c r="C252" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A253" s="12">
+        <v>2</v>
+      </c>
+      <c r="B253" s="15">
+        <v>1</v>
+      </c>
+      <c r="C253" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A254" s="13">
+        <v>2</v>
+      </c>
+      <c r="B254" s="16">
+        <v>1</v>
+      </c>
+      <c r="C254" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A255" s="12">
+        <v>2</v>
+      </c>
+      <c r="B255" s="15">
+        <v>2</v>
+      </c>
+      <c r="C255" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A256" s="13">
+        <v>3</v>
+      </c>
+      <c r="B256" s="16">
+        <v>1</v>
+      </c>
+      <c r="C256" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A257" s="12">
+        <v>2</v>
+      </c>
+      <c r="B257" s="15">
+        <v>1</v>
+      </c>
+      <c r="C257" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A258" s="13">
+        <v>1</v>
+      </c>
+      <c r="B258" s="16">
+        <v>2</v>
+      </c>
+      <c r="C258" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A259" s="12">
+        <v>2</v>
+      </c>
+      <c r="B259" s="15">
+        <v>2</v>
+      </c>
+      <c r="C259" s="19"/>
+    </row>
+    <row r="260" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A260" s="13">
+        <v>2</v>
+      </c>
+      <c r="B260" s="16">
+        <v>1</v>
+      </c>
+      <c r="C260" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A261" s="12">
+        <v>2</v>
+      </c>
+      <c r="B261" s="15">
+        <v>1</v>
+      </c>
+      <c r="C261" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A262" s="13">
+        <v>2</v>
+      </c>
+      <c r="B262" s="16">
+        <v>1</v>
+      </c>
+      <c r="C262" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A263" s="12">
+        <v>1</v>
+      </c>
+      <c r="B263" s="15">
+        <v>1</v>
+      </c>
+      <c r="C263" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A264" s="13">
+        <v>2</v>
+      </c>
+      <c r="B264" s="16">
+        <v>1</v>
+      </c>
+      <c r="C264" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A265" s="12">
+        <v>2</v>
+      </c>
+      <c r="B265" s="15">
+        <v>1</v>
+      </c>
+      <c r="C265" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A266" s="13">
+        <v>2</v>
+      </c>
+      <c r="B266" s="16">
+        <v>1</v>
+      </c>
+      <c r="C266" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A267" s="12">
+        <v>3</v>
+      </c>
+      <c r="B267" s="15">
+        <v>1</v>
+      </c>
+      <c r="C267" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A268" s="13">
+        <v>3</v>
+      </c>
+      <c r="B268" s="16">
+        <v>1</v>
+      </c>
+      <c r="C268" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A269" s="12">
+        <v>2</v>
+      </c>
+      <c r="B269" s="15">
+        <v>2</v>
+      </c>
+      <c r="C269" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A270" s="13">
+        <v>1</v>
+      </c>
+      <c r="B270" s="16">
+        <v>1</v>
+      </c>
+      <c r="C270" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A271" s="12">
+        <v>2</v>
+      </c>
+      <c r="B271" s="15">
+        <v>2</v>
+      </c>
+      <c r="C271" s="19"/>
+    </row>
+    <row r="272" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A272" s="13">
+        <v>1</v>
+      </c>
+      <c r="B272" s="16">
+        <v>2</v>
+      </c>
+      <c r="C272" s="17"/>
+    </row>
+    <row r="273" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A273" s="12">
+        <v>1</v>
+      </c>
+      <c r="B273" s="15">
+        <v>1</v>
+      </c>
+      <c r="C273" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A274" s="13">
+        <v>2</v>
+      </c>
+      <c r="B274" s="16">
+        <v>2</v>
+      </c>
+      <c r="C274" s="17"/>
+    </row>
+    <row r="275" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A275" s="12">
+        <v>3</v>
+      </c>
+      <c r="B275" s="15">
+        <v>1</v>
+      </c>
+      <c r="C275" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A276" s="13">
+        <v>2</v>
+      </c>
+      <c r="B276" s="16">
+        <v>1</v>
+      </c>
+      <c r="C276" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A277" s="12">
+        <v>2</v>
+      </c>
+      <c r="B277" s="15">
+        <v>1</v>
+      </c>
+      <c r="C277" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A278" s="13">
+        <v>2</v>
+      </c>
+      <c r="B278" s="16">
+        <v>1</v>
+      </c>
+      <c r="C278" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A279" s="12">
+        <v>2</v>
+      </c>
+      <c r="B279" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C279" s="19"/>
+    </row>
+    <row r="280" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A280" s="13">
+        <v>1</v>
+      </c>
+      <c r="B280" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" s="17"/>
+    </row>
+    <row r="281" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A281" s="12">
+        <v>1</v>
+      </c>
+      <c r="B281" s="15">
+        <v>1</v>
+      </c>
+      <c r="C281" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A282" s="13">
+        <v>1</v>
+      </c>
+      <c r="B282" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C282" s="17"/>
+    </row>
+    <row r="283" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A283" s="12">
+        <v>3</v>
+      </c>
+      <c r="B283" s="15">
+        <v>1</v>
+      </c>
+      <c r="C283" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A284" s="13">
+        <v>2</v>
+      </c>
+      <c r="B284" s="16">
+        <v>1</v>
+      </c>
+      <c r="C284" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A285" s="12">
+        <v>3</v>
+      </c>
+      <c r="B285" s="15">
+        <v>1</v>
+      </c>
+      <c r="C285" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A286" s="13">
+        <v>1</v>
+      </c>
+      <c r="B286" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C286" s="17"/>
+    </row>
+    <row r="287" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A287" s="12">
+        <v>1</v>
+      </c>
+      <c r="B287" s="15">
+        <v>1</v>
+      </c>
+      <c r="C287" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A288" s="13">
+        <v>2</v>
+      </c>
+      <c r="B288" s="16">
+        <v>1</v>
+      </c>
+      <c r="C288" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A289" s="12">
+        <v>1</v>
+      </c>
+      <c r="B289" s="19"/>
+      <c r="C289" s="19"/>
+    </row>
+    <row r="290" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A290" s="13">
+        <v>2</v>
+      </c>
+      <c r="B290" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C290" s="17"/>
+    </row>
+    <row r="291" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A291" s="12">
+        <v>2</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C291" s="19"/>
+    </row>
+    <row r="292" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A292" s="13">
+        <v>2</v>
+      </c>
+      <c r="B292" s="16">
+        <v>1</v>
+      </c>
+      <c r="C292" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A293" s="12">
+        <v>1</v>
+      </c>
+      <c r="B293" s="15">
+        <v>1</v>
+      </c>
+      <c r="C293" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A294" s="13">
+        <v>1</v>
+      </c>
+      <c r="B294" s="16">
+        <v>1</v>
+      </c>
+      <c r="C294" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="12">
+        <v>1</v>
+      </c>
+      <c r="B295" s="15">
+        <v>1</v>
+      </c>
+      <c r="C295" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="13">
+        <v>2</v>
+      </c>
+      <c r="B296" s="16">
+        <v>1</v>
+      </c>
+      <c r="C296" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A297" s="12">
+        <v>2</v>
+      </c>
+      <c r="B297" s="15">
+        <v>1</v>
+      </c>
+      <c r="C297" s="19"/>
+    </row>
+    <row r="298" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A298" s="13">
+        <v>1</v>
+      </c>
+      <c r="B298" s="16">
+        <v>1</v>
+      </c>
+      <c r="C298" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A299" s="12">
+        <v>2</v>
+      </c>
+      <c r="B299" s="15">
+        <v>1</v>
+      </c>
+      <c r="C299" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A300" s="13">
+        <v>2</v>
+      </c>
+      <c r="B300" s="16">
+        <v>1</v>
+      </c>
+      <c r="C300" s="17"/>
+    </row>
+    <row r="301" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="12">
+        <v>2</v>
+      </c>
+      <c r="B301" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C301" s="19"/>
+    </row>
+    <row r="302" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="13">
+        <v>3</v>
+      </c>
+      <c r="B302" s="16">
+        <v>1</v>
+      </c>
+      <c r="C302" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="12">
+        <v>2</v>
+      </c>
+      <c r="B303" s="15">
+        <v>1</v>
+      </c>
+      <c r="C303" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A304" s="13">
+        <v>2</v>
+      </c>
+      <c r="B304" s="16">
+        <v>1</v>
+      </c>
+      <c r="C304" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A305" s="12">
+        <v>1</v>
+      </c>
+      <c r="B305" s="15">
+        <v>2</v>
+      </c>
+      <c r="C305" s="19"/>
+    </row>
+    <row r="306" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A306" s="13">
+        <v>1</v>
+      </c>
+      <c r="B306" s="16">
+        <v>1</v>
+      </c>
+      <c r="C306" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A307" s="12">
+        <v>2</v>
+      </c>
+      <c r="B307" s="15">
+        <v>1</v>
+      </c>
+      <c r="C307" s="19"/>
+    </row>
+    <row r="308" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A308" s="13">
+        <v>2</v>
+      </c>
+      <c r="B308" s="16">
+        <v>2</v>
+      </c>
+      <c r="C308" s="17"/>
+    </row>
+    <row r="309" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A309" s="12">
+        <v>3</v>
+      </c>
+      <c r="B309" s="15">
+        <v>1</v>
+      </c>
+      <c r="C309" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A310" s="13">
+        <v>2</v>
+      </c>
+      <c r="B310" s="16">
+        <v>1</v>
+      </c>
+      <c r="C310" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A311" s="12">
+        <v>2</v>
+      </c>
+      <c r="B311" s="15">
+        <v>1</v>
+      </c>
+      <c r="C311" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A312" s="13">
+        <v>2</v>
+      </c>
+      <c r="B312" s="16">
+        <v>1</v>
+      </c>
+      <c r="C312" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A313" s="12">
+        <v>1</v>
+      </c>
+      <c r="B313" s="15">
+        <v>1</v>
+      </c>
+      <c r="C313" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A314" s="13">
+        <v>2</v>
+      </c>
+      <c r="B314" s="16">
+        <v>1</v>
+      </c>
+      <c r="C314" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A315" s="12">
+        <v>1</v>
+      </c>
+      <c r="B315" s="15">
+        <v>1</v>
+      </c>
+      <c r="C315" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A316" s="13">
+        <v>3</v>
+      </c>
+      <c r="B316" s="16">
+        <v>1</v>
+      </c>
+      <c r="C316" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A317" s="12">
+        <v>2</v>
+      </c>
+      <c r="B317" s="15">
+        <v>2</v>
+      </c>
+      <c r="C317" s="19"/>
+    </row>
+    <row r="318" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A318" s="13">
+        <v>2</v>
+      </c>
+      <c r="B318" s="16">
+        <v>1</v>
+      </c>
+      <c r="C318" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A319" s="12">
+        <v>2</v>
+      </c>
+      <c r="B319" s="15">
+        <v>1</v>
+      </c>
+      <c r="C319" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A320" s="13">
+        <v>3</v>
+      </c>
+      <c r="B320" s="16">
+        <v>1</v>
+      </c>
+      <c r="C320" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A321" s="12">
+        <v>2</v>
+      </c>
+      <c r="B321" s="15">
+        <v>1</v>
+      </c>
+      <c r="C321" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A322" s="13">
+        <v>2</v>
+      </c>
+      <c r="B322" s="16">
+        <v>1</v>
+      </c>
+      <c r="C322" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A323" s="12">
+        <v>1</v>
+      </c>
+      <c r="B323" s="15">
+        <v>1</v>
+      </c>
+      <c r="C323" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A324" s="13">
+        <v>2</v>
+      </c>
+      <c r="B324" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C324" s="17"/>
+    </row>
+    <row r="325" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A325" s="12">
+        <v>1</v>
+      </c>
+      <c r="B325" s="15">
+        <v>1</v>
+      </c>
+      <c r="C325" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A326" s="13">
+        <v>2</v>
+      </c>
+      <c r="B326" s="17"/>
+      <c r="C326" s="17"/>
+    </row>
+    <row r="327" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A327" s="12">
+        <v>1</v>
+      </c>
+      <c r="B327" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C327" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A328" s="13">
+        <v>2</v>
+      </c>
+      <c r="B328" s="16">
+        <v>1</v>
+      </c>
+      <c r="C328" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A329" s="12">
+        <v>1</v>
+      </c>
+      <c r="B329" s="15">
+        <v>1</v>
+      </c>
+      <c r="C329" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A330" s="13">
+        <v>1</v>
+      </c>
+      <c r="B330" s="16">
+        <v>1</v>
+      </c>
+      <c r="C330" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A331" s="12">
+        <v>3</v>
+      </c>
+      <c r="B331" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C331" s="19"/>
+    </row>
+    <row r="332" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A332" s="13">
+        <v>2</v>
+      </c>
+      <c r="B332" s="16">
+        <v>1</v>
+      </c>
+      <c r="C332" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A333" s="12">
+        <v>1</v>
+      </c>
+      <c r="B333" s="15">
+        <v>1</v>
+      </c>
+      <c r="C333" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A334" s="13">
+        <v>3</v>
+      </c>
+      <c r="B334" s="16">
+        <v>1</v>
+      </c>
+      <c r="C334" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A335" s="12">
+        <v>2</v>
+      </c>
+      <c r="B335" s="15">
+        <v>1</v>
+      </c>
+      <c r="C335" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A336" s="13">
+        <v>3</v>
+      </c>
+      <c r="B336" s="16">
+        <v>1</v>
+      </c>
+      <c r="C336" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A337" s="12">
+        <v>3</v>
+      </c>
+      <c r="B337" s="15">
+        <v>1</v>
+      </c>
+      <c r="C337" s="19"/>
+    </row>
+    <row r="338" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A338" s="13">
+        <v>1</v>
+      </c>
+      <c r="B338" s="16">
+        <v>1</v>
+      </c>
+      <c r="C338" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A339" s="12">
+        <v>1</v>
+      </c>
+      <c r="B339" s="15">
+        <v>1</v>
+      </c>
+      <c r="C339" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A340" s="13">
+        <v>1</v>
+      </c>
+      <c r="B340" s="17"/>
+      <c r="C340" s="17"/>
+    </row>
+    <row r="341" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A341" s="12">
+        <v>2</v>
+      </c>
+      <c r="B341" s="15">
+        <v>1</v>
+      </c>
+      <c r="C341" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A342" s="13">
+        <v>3</v>
+      </c>
+      <c r="B342" s="16">
+        <v>1</v>
+      </c>
+      <c r="C342" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A343" s="12">
+        <v>1</v>
+      </c>
+      <c r="B343" s="15">
+        <v>1</v>
+      </c>
+      <c r="C343" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A344" s="13">
+        <v>3</v>
+      </c>
+      <c r="B344" s="16">
+        <v>1</v>
+      </c>
+      <c r="C344" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A345" s="12">
+        <v>2</v>
+      </c>
+      <c r="B345" s="15">
+        <v>1</v>
+      </c>
+      <c r="C345" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A346" s="13">
+        <v>1</v>
+      </c>
+      <c r="B346" s="16">
+        <v>1</v>
+      </c>
+      <c r="C346" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A347" s="12">
+        <v>3</v>
+      </c>
+      <c r="B347" s="15">
+        <v>1</v>
+      </c>
+      <c r="C347" s="19"/>
+    </row>
+    <row r="348" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A348" s="13">
+        <v>2</v>
+      </c>
+      <c r="B348" s="16">
+        <v>1</v>
+      </c>
+      <c r="C348" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A349" s="12">
+        <v>2</v>
+      </c>
+      <c r="B349" s="15">
+        <v>1</v>
+      </c>
+      <c r="C349" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A350" s="13">
+        <v>1</v>
+      </c>
+      <c r="B350" s="16">
+        <v>1</v>
+      </c>
+      <c r="C350" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A351" s="12">
+        <v>1</v>
+      </c>
+      <c r="B351" s="15">
+        <v>1</v>
+      </c>
+      <c r="C351" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A352" s="13">
+        <v>2</v>
+      </c>
+      <c r="B352" s="16">
+        <v>1</v>
+      </c>
+      <c r="C352" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A353" s="12">
+        <v>1</v>
+      </c>
+      <c r="B353" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C353" s="19"/>
+    </row>
+    <row r="354" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A354" s="13">
+        <v>2</v>
+      </c>
+      <c r="B354" s="16">
+        <v>1</v>
+      </c>
+      <c r="C354" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A355" s="12">
+        <v>2</v>
+      </c>
+      <c r="B355" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C355" s="19"/>
+    </row>
+    <row r="356" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A356" s="13">
+        <v>2</v>
+      </c>
+      <c r="B356" s="16">
+        <v>1</v>
+      </c>
+      <c r="C356" s="17"/>
+    </row>
+    <row r="357" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A357" s="12">
+        <v>2</v>
+      </c>
+      <c r="B357" s="15">
+        <v>1</v>
+      </c>
+      <c r="C357" s="19"/>
+    </row>
+    <row r="358" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A358" s="13">
+        <v>1</v>
+      </c>
+      <c r="B358" s="16">
+        <v>1</v>
+      </c>
+      <c r="C358" s="17"/>
+    </row>
+    <row r="359" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A359" s="12">
+        <v>2</v>
+      </c>
+      <c r="B359" s="19"/>
+      <c r="C359" s="19"/>
+    </row>
+    <row r="360" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A360" s="13">
+        <v>1</v>
+      </c>
+      <c r="B360" s="16">
+        <v>1</v>
+      </c>
+      <c r="C360" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A361" s="12">
+        <v>2</v>
+      </c>
+      <c r="B361" s="19"/>
+      <c r="C361" s="19"/>
+    </row>
+    <row r="362" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A362" s="13">
+        <v>1</v>
+      </c>
+      <c r="B362" s="17"/>
+      <c r="C362" s="17"/>
+    </row>
+    <row r="363" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A363" s="12">
+        <v>2</v>
+      </c>
+      <c r="B363" s="19"/>
+      <c r="C363" s="19"/>
+    </row>
+    <row r="364" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A364" s="13">
+        <v>2</v>
+      </c>
+      <c r="B364" s="16">
+        <v>1</v>
+      </c>
+      <c r="C364" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A365" s="12">
+        <v>1</v>
+      </c>
+      <c r="B365" s="15">
+        <v>1</v>
+      </c>
+      <c r="C365" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A366" s="13">
+        <v>2</v>
+      </c>
+      <c r="B366" s="16">
+        <v>1</v>
+      </c>
+      <c r="C366" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A367" s="12">
+        <v>1</v>
+      </c>
+      <c r="B367" s="19"/>
+      <c r="C367" s="19"/>
+    </row>
+    <row r="368" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A368" s="13">
+        <v>1</v>
+      </c>
+      <c r="B368" s="16">
+        <v>1</v>
+      </c>
+      <c r="C368" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A369" s="12">
+        <v>1</v>
+      </c>
+      <c r="B369" s="15">
+        <v>1</v>
+      </c>
+      <c r="C369" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A370" s="13">
+        <v>2</v>
+      </c>
+      <c r="B370" s="16">
+        <v>1</v>
+      </c>
+      <c r="C370" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A371" s="12">
+        <v>2</v>
+      </c>
+      <c r="B371" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C371" s="19"/>
+    </row>
+    <row r="372" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A372" s="13">
+        <v>1</v>
+      </c>
+      <c r="B372" s="16">
+        <v>1</v>
+      </c>
+      <c r="C372" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A373" s="12">
+        <v>3</v>
+      </c>
+      <c r="B373" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C373" s="19"/>
+    </row>
+    <row r="374" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A374" s="13">
+        <v>2</v>
+      </c>
+      <c r="B374" s="16">
+        <v>1</v>
+      </c>
+      <c r="C374" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A375" s="12">
+        <v>2</v>
+      </c>
+      <c r="B375" s="15">
+        <v>1</v>
+      </c>
+      <c r="C375" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A376" s="13">
+        <v>2</v>
+      </c>
+      <c r="B376" s="16">
+        <v>1</v>
+      </c>
+      <c r="C376" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A377" s="12">
+        <v>1</v>
+      </c>
+      <c r="B377" s="19"/>
+      <c r="C377" s="19"/>
+    </row>
+    <row r="378" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A378" s="13">
+        <v>1</v>
+      </c>
+      <c r="B378" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C378" s="17"/>
+    </row>
+    <row r="379" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A379" s="12">
+        <v>3</v>
+      </c>
+      <c r="B379" s="15">
+        <v>1</v>
+      </c>
+      <c r="C379" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A380" s="13">
+        <v>1</v>
+      </c>
+      <c r="B380" s="16">
+        <v>1</v>
+      </c>
+      <c r="C380" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A381" s="12">
+        <v>1</v>
+      </c>
+      <c r="B381" s="15">
+        <v>1</v>
+      </c>
+      <c r="C381" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A382" s="13">
+        <v>2</v>
+      </c>
+      <c r="B382" s="16">
+        <v>2</v>
+      </c>
+      <c r="C382" s="17"/>
+    </row>
+    <row r="383" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A383" s="12">
+        <v>3</v>
+      </c>
+      <c r="B383" s="15">
+        <v>1</v>
+      </c>
+      <c r="C383" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A384" s="13">
+        <v>1</v>
+      </c>
+      <c r="B384" s="16">
+        <v>1</v>
+      </c>
+      <c r="C384" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A385" s="12">
+        <v>2</v>
+      </c>
+      <c r="B385" s="15">
+        <v>2</v>
+      </c>
+      <c r="C385" s="19"/>
+    </row>
+    <row r="386" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A386" s="13">
+        <v>1</v>
+      </c>
+      <c r="B386" s="16">
+        <v>2</v>
+      </c>
+      <c r="C386" s="17"/>
+    </row>
+    <row r="387" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A387" s="12">
+        <v>1</v>
+      </c>
+      <c r="B387" s="15">
+        <v>1</v>
+      </c>
+      <c r="C387" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A388" s="13">
+        <v>1</v>
+      </c>
+      <c r="B388" s="16">
+        <v>1</v>
+      </c>
+      <c r="C388" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A389" s="12">
+        <v>2</v>
+      </c>
+      <c r="B389" s="15">
+        <v>1</v>
+      </c>
+      <c r="C389" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A390" s="13">
+        <v>2</v>
+      </c>
+      <c r="B390" s="16">
+        <v>1</v>
+      </c>
+      <c r="C390" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A391" s="12">
+        <v>3</v>
+      </c>
+      <c r="B391" s="15">
+        <v>1</v>
+      </c>
+      <c r="C391" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A392" s="13">
+        <v>1</v>
+      </c>
+      <c r="B392" s="16">
+        <v>1</v>
+      </c>
+      <c r="C392" s="17"/>
+    </row>
+    <row r="393" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A393" s="12">
+        <v>2</v>
+      </c>
+      <c r="B393" s="15">
+        <v>2</v>
+      </c>
+      <c r="C393" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A394" s="13">
+        <v>2</v>
+      </c>
+      <c r="B394" s="16">
+        <v>1</v>
+      </c>
+      <c r="C394" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A395" s="12">
+        <v>3</v>
+      </c>
+      <c r="B395" s="15">
+        <v>1</v>
+      </c>
+      <c r="C395" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A396" s="13">
+        <v>1</v>
+      </c>
+      <c r="B396" s="16">
+        <v>1</v>
+      </c>
+      <c r="C396" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A397" s="12">
+        <v>3</v>
+      </c>
+      <c r="B397" s="15">
+        <v>1</v>
+      </c>
+      <c r="C397" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A398" s="13">
+        <v>2</v>
+      </c>
+      <c r="B398" s="16">
+        <v>2</v>
+      </c>
+      <c r="C398" s="17"/>
+    </row>
+    <row r="399" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A399" s="12">
+        <v>2</v>
+      </c>
+      <c r="B399" s="15">
+        <v>1</v>
+      </c>
+      <c r="C399" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A400" s="13">
+        <v>2</v>
+      </c>
+      <c r="B400" s="16">
+        <v>1</v>
+      </c>
+      <c r="C400" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A401" s="12">
+        <v>2</v>
+      </c>
+      <c r="B401" s="15">
+        <v>1</v>
+      </c>
+      <c r="C401" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A402" s="13">
+        <v>2</v>
+      </c>
+      <c r="B402" s="16">
+        <v>1</v>
+      </c>
+      <c r="C402" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A403" s="12">
+        <v>2</v>
+      </c>
+      <c r="B403" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C403" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A404" s="13">
+        <v>1</v>
+      </c>
+      <c r="B404" s="16">
+        <v>1</v>
+      </c>
+      <c r="C404" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A405" s="12">
+        <v>3</v>
+      </c>
+      <c r="B405" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C405" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A406" s="13">
+        <v>2</v>
+      </c>
+      <c r="B406" s="16">
+        <v>2</v>
+      </c>
+      <c r="C406" s="17"/>
+    </row>
+    <row r="407" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A407" s="12">
+        <v>1</v>
+      </c>
+      <c r="B407" s="15">
+        <v>1</v>
+      </c>
+      <c r="C407" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A408" s="13">
+        <v>2</v>
+      </c>
+      <c r="B408" s="16">
+        <v>2</v>
+      </c>
+      <c r="C408" s="17"/>
+    </row>
+    <row r="409" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A409" s="12">
+        <v>1</v>
+      </c>
+      <c r="B409" s="15">
+        <v>2</v>
+      </c>
+      <c r="C409" s="19"/>
+    </row>
+    <row r="410" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A410" s="13">
+        <v>2</v>
+      </c>
+      <c r="B410" s="16">
+        <v>1</v>
+      </c>
+      <c r="C410" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A411" s="12">
+        <v>2</v>
+      </c>
+      <c r="B411" s="15">
+        <v>2</v>
+      </c>
+      <c r="C411" s="19"/>
+    </row>
+    <row r="412" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A412" s="13">
+        <v>2</v>
+      </c>
+      <c r="B412" s="16">
+        <v>1</v>
+      </c>
+      <c r="C412" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A413" s="12">
+        <v>1</v>
+      </c>
+      <c r="B413" s="15">
+        <v>1</v>
+      </c>
+      <c r="C413" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A414" s="13">
+        <v>1</v>
+      </c>
+      <c r="B414" s="16">
+        <v>1</v>
+      </c>
+      <c r="C414" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A415" s="12">
+        <v>3</v>
+      </c>
+      <c r="B415" s="15">
+        <v>1</v>
+      </c>
+      <c r="C415" s="19"/>
+    </row>
+    <row r="416" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A416" s="13">
+        <v>2</v>
+      </c>
+      <c r="B416" s="16">
+        <v>1</v>
+      </c>
+      <c r="C416" s="17"/>
+    </row>
+    <row r="417" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A417" s="12">
+        <v>2</v>
+      </c>
+      <c r="B417" s="15">
+        <v>1</v>
+      </c>
+      <c r="C417" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A418" s="13">
+        <v>2</v>
+      </c>
+      <c r="B418" s="16">
+        <v>1</v>
+      </c>
+      <c r="C418" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A419" s="12">
+        <v>1</v>
+      </c>
+      <c r="B419" s="15">
+        <v>1</v>
+      </c>
+      <c r="C419" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A420" s="13">
+        <v>2</v>
+      </c>
+      <c r="B420" s="16">
+        <v>1</v>
+      </c>
+      <c r="C420" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A421" s="12">
+        <v>2</v>
+      </c>
+      <c r="B421" s="15">
+        <v>1</v>
+      </c>
+      <c r="C421" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A422" s="13">
+        <v>3</v>
+      </c>
+      <c r="B422" s="16">
+        <v>2</v>
+      </c>
+      <c r="C422" s="17"/>
+    </row>
+    <row r="423" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A423" s="12">
+        <v>1</v>
+      </c>
+      <c r="B423" s="15">
+        <v>1</v>
+      </c>
+      <c r="C423" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A424" s="13">
+        <v>2</v>
+      </c>
+      <c r="B424" s="16">
+        <v>2</v>
+      </c>
+      <c r="C424" s="17"/>
+    </row>
+    <row r="425" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A425" s="12">
+        <v>1</v>
+      </c>
+      <c r="B425" s="15">
+        <v>1</v>
+      </c>
+      <c r="C425" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A426" s="13">
+        <v>2</v>
+      </c>
+      <c r="B426" s="16">
+        <v>2</v>
+      </c>
+      <c r="C426" s="17"/>
+    </row>
+    <row r="427" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A427" s="12">
+        <v>3</v>
+      </c>
+      <c r="B427" s="15">
+        <v>1</v>
+      </c>
+      <c r="C427" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A428" s="13">
+        <v>2</v>
+      </c>
+      <c r="B428" s="16">
+        <v>2</v>
+      </c>
+      <c r="C428" s="17"/>
+    </row>
+    <row r="429" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A429" s="12">
+        <v>2</v>
+      </c>
+      <c r="B429" s="15">
+        <v>2</v>
+      </c>
+      <c r="C429" s="19"/>
+    </row>
+    <row r="430" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A430" s="13">
+        <v>2</v>
+      </c>
+      <c r="B430" s="16">
+        <v>2</v>
+      </c>
+      <c r="C430" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A431" s="12">
+        <v>1</v>
+      </c>
+      <c r="B431" s="15">
+        <v>1</v>
+      </c>
+      <c r="C431" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A432" s="13">
+        <v>1</v>
+      </c>
+      <c r="B432" s="16">
+        <v>1</v>
+      </c>
+      <c r="C432" s="17"/>
+    </row>
+    <row r="433" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A433" s="12">
+        <v>2</v>
+      </c>
+      <c r="B433" s="15">
+        <v>1</v>
+      </c>
+      <c r="C433" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A434" s="13">
+        <v>1</v>
+      </c>
+      <c r="B434" s="16">
+        <v>2</v>
+      </c>
+      <c r="C434" s="17"/>
+    </row>
+    <row r="435" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A435" s="12">
+        <v>1</v>
+      </c>
+      <c r="B435" s="15">
+        <v>1</v>
+      </c>
+      <c r="C435" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A436" s="13">
+        <v>2</v>
+      </c>
+      <c r="B436" s="16">
+        <v>1</v>
+      </c>
+      <c r="C436" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A437" s="12">
+        <v>1</v>
+      </c>
+      <c r="B437" s="15">
+        <v>1</v>
+      </c>
+      <c r="C437" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A438" s="13">
+        <v>2</v>
+      </c>
+      <c r="B438" s="16">
+        <v>1</v>
+      </c>
+      <c r="C438" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A439" s="12">
+        <v>1</v>
+      </c>
+      <c r="B439" s="15">
+        <v>1</v>
+      </c>
+      <c r="C439" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A440" s="13">
+        <v>1</v>
+      </c>
+      <c r="B440" s="16">
+        <v>1</v>
+      </c>
+      <c r="C440" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A441" s="12">
+        <v>2</v>
+      </c>
+      <c r="B441" s="15">
+        <v>1</v>
+      </c>
+      <c r="C441" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A442" s="13">
+        <v>1</v>
+      </c>
+      <c r="B442" s="16">
+        <v>1</v>
+      </c>
+      <c r="C442" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A443" s="12">
+        <v>2</v>
+      </c>
+      <c r="B443" s="15">
+        <v>1</v>
+      </c>
+      <c r="C443" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A444" s="13">
+        <v>1</v>
+      </c>
+      <c r="B444" s="16">
+        <v>1</v>
+      </c>
+      <c r="C444" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A445" s="12">
+        <v>2</v>
+      </c>
+      <c r="B445" s="15">
+        <v>1</v>
+      </c>
+      <c r="C445" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A446" s="13">
+        <v>2</v>
+      </c>
+      <c r="B446" s="16">
+        <v>1</v>
+      </c>
+      <c r="C446" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A447" s="12">
+        <v>2</v>
+      </c>
+      <c r="B447" s="19"/>
+      <c r="C447" s="19"/>
+    </row>
+    <row r="448" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A448" s="13">
+        <v>2</v>
+      </c>
+      <c r="B448" s="16">
+        <v>1</v>
+      </c>
+      <c r="C448" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A449" s="12">
+        <v>3</v>
+      </c>
+      <c r="B449" s="15">
+        <v>1</v>
+      </c>
+      <c r="C449" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A450" s="13">
+        <v>2</v>
+      </c>
+      <c r="B450" s="16">
+        <v>1</v>
+      </c>
+      <c r="C450" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A451" s="12">
+        <v>1</v>
+      </c>
+      <c r="B451" s="15">
+        <v>1</v>
+      </c>
+      <c r="C451" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A452" s="13">
+        <v>2</v>
+      </c>
+      <c r="B452" s="16">
+        <v>1</v>
+      </c>
+      <c r="C452" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A453" s="12">
+        <v>1</v>
+      </c>
+      <c r="B453" s="15">
+        <v>1</v>
+      </c>
+      <c r="C453" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A454" s="13">
+        <v>3</v>
+      </c>
+      <c r="B454" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="156.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="12">
-        <v>1</v>
-      </c>
-      <c r="B138" s="15" t="s">
+      <c r="C454" s="17"/>
+    </row>
+    <row r="455" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A455" s="12">
+        <v>3</v>
+      </c>
+      <c r="B455" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C455" s="19"/>
+    </row>
+    <row r="456" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A456" s="13">
+        <v>1</v>
+      </c>
+      <c r="B456" s="16">
+        <v>1</v>
+      </c>
+      <c r="C456" s="17"/>
+    </row>
+    <row r="457" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A457" s="12">
+        <v>1</v>
+      </c>
+      <c r="B457" s="15">
+        <v>1</v>
+      </c>
+      <c r="C457" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A458" s="13">
+        <v>1</v>
+      </c>
+      <c r="B458" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C138" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="13">
-        <v>2</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C139" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="12">
-        <v>2</v>
-      </c>
-      <c r="B140" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="13">
-        <v>3</v>
-      </c>
-      <c r="B141" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C141" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="12">
-        <v>3</v>
-      </c>
-      <c r="B142" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C142" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="13">
-        <v>1</v>
-      </c>
-      <c r="B143" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C143" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="12">
-        <v>1</v>
-      </c>
-      <c r="B144" s="15" t="s">
+      <c r="C458" s="17"/>
+    </row>
+    <row r="459" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A459" s="12">
+        <v>1</v>
+      </c>
+      <c r="B459" s="15">
+        <v>1</v>
+      </c>
+      <c r="C459" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A460" s="13">
+        <v>1</v>
+      </c>
+      <c r="B460" s="16">
+        <v>1</v>
+      </c>
+      <c r="C460" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A461" s="12">
+        <v>1</v>
+      </c>
+      <c r="B461" s="15">
+        <v>1</v>
+      </c>
+      <c r="C461" s="19"/>
+    </row>
+    <row r="462" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A462" s="13">
+        <v>1</v>
+      </c>
+      <c r="B462" s="16">
+        <v>1</v>
+      </c>
+      <c r="C462" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A463" s="12">
+        <v>1</v>
+      </c>
+      <c r="B463" s="15">
+        <v>1</v>
+      </c>
+      <c r="C463" s="19"/>
+    </row>
+    <row r="464" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A464" s="13">
+        <v>2</v>
+      </c>
+      <c r="B464" s="16">
+        <v>1</v>
+      </c>
+      <c r="C464" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A465" s="12">
+        <v>1</v>
+      </c>
+      <c r="B465" s="15">
+        <v>1</v>
+      </c>
+      <c r="C465" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A466" s="13">
+        <v>2</v>
+      </c>
+      <c r="B466" s="16">
+        <v>1</v>
+      </c>
+      <c r="C466" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A467" s="12">
+        <v>2</v>
+      </c>
+      <c r="B467" s="15">
+        <v>1</v>
+      </c>
+      <c r="C467" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A468" s="13">
+        <v>1</v>
+      </c>
+      <c r="B468" s="16">
+        <v>1</v>
+      </c>
+      <c r="C468" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A469" s="12">
+        <v>1</v>
+      </c>
+      <c r="B469" s="15">
+        <v>1</v>
+      </c>
+      <c r="C469" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A470" s="13">
+        <v>1</v>
+      </c>
+      <c r="B470" s="16">
+        <v>1</v>
+      </c>
+      <c r="C470" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A471" s="12">
+        <v>2</v>
+      </c>
+      <c r="B471" s="15">
+        <v>2</v>
+      </c>
+      <c r="C471" s="19"/>
+    </row>
+    <row r="472" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A472" s="13">
+        <v>1</v>
+      </c>
+      <c r="B472" s="16">
+        <v>2</v>
+      </c>
+      <c r="C472" s="17"/>
+    </row>
+    <row r="473" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A473" s="12">
+        <v>1</v>
+      </c>
+      <c r="B473" s="15">
+        <v>1</v>
+      </c>
+      <c r="C473" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A474" s="13">
+        <v>2</v>
+      </c>
+      <c r="B474" s="16">
+        <v>1</v>
+      </c>
+      <c r="C474" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A475" s="12">
+        <v>3</v>
+      </c>
+      <c r="B475" s="15">
+        <v>1</v>
+      </c>
+      <c r="C475" s="19"/>
+    </row>
+    <row r="476" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A476" s="13">
+        <v>1</v>
+      </c>
+      <c r="B476" s="16">
+        <v>1</v>
+      </c>
+      <c r="C476" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A477" s="12">
+        <v>1</v>
+      </c>
+      <c r="B477" s="15">
+        <v>1</v>
+      </c>
+      <c r="C477" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A478" s="13">
+        <v>1</v>
+      </c>
+      <c r="B478" s="16">
+        <v>1</v>
+      </c>
+      <c r="C478" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A479" s="12">
+        <v>1</v>
+      </c>
+      <c r="B479" s="15">
+        <v>1</v>
+      </c>
+      <c r="C479" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A480" s="13">
+        <v>1</v>
+      </c>
+      <c r="B480" s="16">
+        <v>2</v>
+      </c>
+      <c r="C480" s="17"/>
+    </row>
+    <row r="481" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A481" s="12">
+        <v>1</v>
+      </c>
+      <c r="B481" s="15">
+        <v>1</v>
+      </c>
+      <c r="C481" s="19"/>
+    </row>
+    <row r="482" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A482" s="13">
+        <v>1</v>
+      </c>
+      <c r="B482" s="16">
+        <v>1</v>
+      </c>
+      <c r="C482" s="17"/>
+    </row>
+    <row r="483" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A483" s="12">
+        <v>2</v>
+      </c>
+      <c r="B483" s="15">
+        <v>2</v>
+      </c>
+      <c r="C483" s="19"/>
+    </row>
+    <row r="484" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A484" s="13">
+        <v>1</v>
+      </c>
+      <c r="B484" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C144" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="13">
-        <v>2</v>
-      </c>
-      <c r="B145" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C145" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="12">
-        <v>2</v>
-      </c>
-      <c r="B146" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C146" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="13">
-        <v>2</v>
-      </c>
-      <c r="B147" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C147" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="12">
-        <v>3</v>
-      </c>
-      <c r="B148" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C148" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="13">
-        <v>2</v>
-      </c>
-      <c r="B149" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C149" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="12">
-        <v>1</v>
-      </c>
-      <c r="B150" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C150" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="13">
-        <v>2</v>
-      </c>
-      <c r="B151" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C151" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="12">
-        <v>2</v>
-      </c>
-      <c r="B152" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C152" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="13">
-        <v>2</v>
-      </c>
-      <c r="B153" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C153" s="17"/>
-    </row>
-    <row r="154" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="12">
-        <v>3</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C154" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="13">
-        <v>1</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C155" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="12">
-        <v>2</v>
-      </c>
-      <c r="B156" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C156" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="13">
-        <v>3</v>
-      </c>
-      <c r="B157" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C157" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="12">
-        <v>3</v>
-      </c>
-      <c r="B158" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C158" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="13">
-        <v>3</v>
-      </c>
-      <c r="B159" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C159" s="17"/>
-    </row>
-    <row r="160" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="12">
-        <v>2</v>
-      </c>
-      <c r="B160" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C160" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="13">
-        <v>1</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C161" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="12">
-        <v>1</v>
-      </c>
-      <c r="B162" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C162" s="19"/>
-    </row>
-    <row r="163" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="13">
-        <v>2</v>
-      </c>
-      <c r="B163" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C163" s="17"/>
-    </row>
-    <row r="164" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="12">
-        <v>1</v>
-      </c>
-      <c r="B164" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C164" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="13">
-        <v>2</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C165" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="12">
-        <v>3</v>
-      </c>
-      <c r="B166" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C166" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="13">
-        <v>3</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C167" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="12">
-        <v>1</v>
-      </c>
-      <c r="B168" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C168" s="19"/>
-    </row>
-    <row r="169" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="13">
-        <v>1</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C169" s="17"/>
-    </row>
-    <row r="170" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="12">
-        <v>2</v>
-      </c>
-      <c r="B170" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C170" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="13">
-        <v>3</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C171" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="12">
-        <v>2</v>
-      </c>
-      <c r="B172" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C172" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="13">
-        <v>1</v>
-      </c>
-      <c r="B173" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C173" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="12">
-        <v>1</v>
-      </c>
-      <c r="B174" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C174" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="13">
-        <v>2</v>
-      </c>
-      <c r="B175" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C175" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="12">
-        <v>2</v>
-      </c>
-      <c r="B176" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C176" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="13">
-        <v>2</v>
-      </c>
-      <c r="B177" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C177" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="12">
-        <v>2</v>
-      </c>
-      <c r="B178" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C178" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="13">
-        <v>3</v>
-      </c>
-      <c r="B179" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C179" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="12">
-        <v>2</v>
-      </c>
-      <c r="B180" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C180" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="13">
-        <v>2</v>
-      </c>
-      <c r="B181" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C181" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="12">
-        <v>2</v>
-      </c>
-      <c r="B182" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C182" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="13">
-        <v>1</v>
-      </c>
-      <c r="B183" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C183" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="12">
-        <v>1</v>
-      </c>
-      <c r="B184" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="13">
-        <v>2</v>
-      </c>
-      <c r="B185" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C185" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="12">
-        <v>3</v>
-      </c>
-      <c r="B186" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C186" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="13">
-        <v>2</v>
-      </c>
-      <c r="B187" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C187" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="12">
-        <v>1</v>
-      </c>
-      <c r="B188" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C188" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="13">
-        <v>2</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C189" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="12">
-        <v>3</v>
-      </c>
-      <c r="B190" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C190" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="13">
-        <v>3</v>
-      </c>
-      <c r="B191" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C191" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="12">
-        <v>3</v>
-      </c>
-      <c r="B192" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C192" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="13">
-        <v>3</v>
-      </c>
-      <c r="B193" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C193" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="12">
-        <v>2</v>
-      </c>
-      <c r="B194" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C194" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="13">
-        <v>3</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C195" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="12">
-        <v>2</v>
-      </c>
-      <c r="B196" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C196" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="13">
-        <v>2</v>
-      </c>
-      <c r="B197" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C197" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="12">
-        <v>2</v>
-      </c>
-      <c r="B198" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C198" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="13">
-        <v>1</v>
-      </c>
-      <c r="B199" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C199" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="12">
-        <v>2</v>
-      </c>
-      <c r="B200" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C200" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="13">
-        <v>2</v>
-      </c>
-      <c r="B201" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C201" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="12">
-        <v>2</v>
-      </c>
-      <c r="B202" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C202" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="13">
-        <v>2</v>
-      </c>
-      <c r="B203" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C203" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="12">
-        <v>1</v>
-      </c>
-      <c r="B204" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C204" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="13">
-        <v>2</v>
-      </c>
-      <c r="B205" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C205" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="12">
-        <v>3</v>
-      </c>
-      <c r="B206" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C206" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="13">
-        <v>2</v>
-      </c>
-      <c r="B207" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C207" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="12">
-        <v>2</v>
-      </c>
-      <c r="B208" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C208" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="13">
-        <v>3</v>
-      </c>
-      <c r="B209" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C209" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="12">
-        <v>3</v>
-      </c>
-      <c r="B210" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C210" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A211" s="13">
-        <v>1</v>
-      </c>
-      <c r="B211" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C211" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A212" s="12">
-        <v>2</v>
-      </c>
-      <c r="B212" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C212" s="19"/>
-    </row>
-    <row r="213" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A213" s="13">
-        <v>2</v>
-      </c>
-      <c r="B213" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C213" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="12">
-        <v>1</v>
-      </c>
-      <c r="B214" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C214" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A215" s="13">
-        <v>1</v>
-      </c>
-      <c r="B215" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C215" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A216" s="12">
-        <v>2</v>
-      </c>
-      <c r="B216" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C216" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="13">
-        <v>2</v>
-      </c>
-      <c r="B217" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C217" s="13">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A218" s="12">
-        <v>2</v>
-      </c>
-      <c r="B218" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C218" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A219" s="13">
-        <v>2</v>
-      </c>
-      <c r="B219" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C219" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="12">
-        <v>2</v>
-      </c>
-      <c r="B220" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C220" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="13">
-        <v>2</v>
-      </c>
-      <c r="B221" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C221" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="12">
-        <v>2</v>
-      </c>
-      <c r="B222" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C222" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="13">
-        <v>2</v>
-      </c>
-      <c r="B223" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C223" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="12">
-        <v>2</v>
-      </c>
-      <c r="B224" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C224" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="13">
-        <v>1</v>
-      </c>
-      <c r="B225" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C225" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A226" s="12">
-        <v>2</v>
-      </c>
-      <c r="B226" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C226" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A227" s="13">
-        <v>2</v>
-      </c>
-      <c r="B227" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C227" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A228" s="12">
-        <v>3</v>
-      </c>
-      <c r="B228" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C228" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A229" s="13">
-        <v>1</v>
-      </c>
-      <c r="B229" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C229" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A230" s="12">
-        <v>2</v>
-      </c>
-      <c r="B230" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C230" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A231" s="13">
-        <v>3</v>
-      </c>
-      <c r="B231" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C231" s="17"/>
-    </row>
-    <row r="232" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A232" s="12">
-        <v>2</v>
-      </c>
-      <c r="B232" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C232" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A233" s="13">
-        <v>1</v>
-      </c>
-      <c r="B233" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C233" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A234" s="12">
-        <v>1</v>
-      </c>
-      <c r="B234" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C234" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A235" s="13">
-        <v>2</v>
-      </c>
-      <c r="B235" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C235" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A236" s="12">
-        <v>1</v>
-      </c>
-      <c r="B236" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C236" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A237" s="13">
-        <v>1</v>
-      </c>
-      <c r="B237" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C237" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A238" s="12">
-        <v>1</v>
-      </c>
-      <c r="B238" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C238" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A239" s="13">
-        <v>2</v>
-      </c>
-      <c r="B239" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C239" s="17"/>
-    </row>
-    <row r="240" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A240" s="12">
-        <v>1</v>
-      </c>
-      <c r="B240" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C240" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A241" s="13">
-        <v>2</v>
-      </c>
-      <c r="B241" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C241" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A242" s="12">
-        <v>2</v>
-      </c>
-      <c r="B242" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C242" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A243" s="13">
-        <v>1</v>
-      </c>
-      <c r="B243" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C243" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A244" s="12">
-        <v>1</v>
-      </c>
-      <c r="B244" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C244" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="13">
-        <v>1</v>
-      </c>
-      <c r="B245" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C245" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A246" s="12">
-        <v>2</v>
-      </c>
-      <c r="B246" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C246" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A247" s="13">
-        <v>1</v>
-      </c>
-      <c r="B247" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C247" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A248" s="12">
-        <v>1</v>
-      </c>
-      <c r="B248" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C248" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A249" s="13">
-        <v>4</v>
-      </c>
-      <c r="B249" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C249" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A250" s="12">
-        <v>2</v>
-      </c>
-      <c r="B250" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C250" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="117.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A251" s="13">
-        <v>2</v>
-      </c>
-      <c r="B251" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C251" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="12">
-        <v>2</v>
-      </c>
-      <c r="B252" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C252" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="13">
-        <v>1</v>
-      </c>
-      <c r="B253" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C253" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="12">
-        <v>2</v>
-      </c>
-      <c r="B254" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C254" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A255" s="13">
-        <v>2</v>
-      </c>
-      <c r="B255" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C255" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A256" s="12">
-        <v>2</v>
-      </c>
-      <c r="B256" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C256" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A257" s="13">
-        <v>3</v>
-      </c>
-      <c r="B257" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C257" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A258" s="12">
-        <v>2</v>
-      </c>
-      <c r="B258" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C258" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A259" s="13">
-        <v>1</v>
-      </c>
-      <c r="B259" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C259" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A260" s="12">
-        <v>2</v>
-      </c>
-      <c r="B260" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C260" s="19"/>
-    </row>
-    <row r="261" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A261" s="13">
-        <v>2</v>
-      </c>
-      <c r="B261" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C261" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A262" s="12">
-        <v>2</v>
-      </c>
-      <c r="B262" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C262" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A263" s="13">
-        <v>2</v>
-      </c>
-      <c r="B263" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C263" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A264" s="12">
-        <v>1</v>
-      </c>
-      <c r="B264" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C264" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A265" s="13">
-        <v>2</v>
-      </c>
-      <c r="B265" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C265" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A266" s="12">
-        <v>2</v>
-      </c>
-      <c r="B266" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C266" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A267" s="13">
-        <v>2</v>
-      </c>
-      <c r="B267" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C267" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A268" s="12">
-        <v>3</v>
-      </c>
-      <c r="B268" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C268" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A269" s="13">
-        <v>3</v>
-      </c>
-      <c r="B269" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C269" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A270" s="12">
-        <v>2</v>
-      </c>
-      <c r="B270" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C270" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A271" s="13">
-        <v>1</v>
-      </c>
-      <c r="B271" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C271" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A272" s="12">
-        <v>2</v>
-      </c>
-      <c r="B272" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C272" s="19"/>
-    </row>
-    <row r="273" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A273" s="13">
-        <v>1</v>
-      </c>
-      <c r="B273" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C273" s="17"/>
-    </row>
-    <row r="274" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A274" s="12">
-        <v>1</v>
-      </c>
-      <c r="B274" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C274" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A275" s="13">
-        <v>2</v>
-      </c>
-      <c r="B275" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C275" s="17"/>
-    </row>
-    <row r="276" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A276" s="12">
-        <v>3</v>
-      </c>
-      <c r="B276" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C276" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A277" s="13">
-        <v>2</v>
-      </c>
-      <c r="B277" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C277" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A278" s="12">
-        <v>2</v>
-      </c>
-      <c r="B278" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C278" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A279" s="13">
-        <v>2</v>
-      </c>
-      <c r="B279" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C279" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A280" s="12">
-        <v>2</v>
-      </c>
-      <c r="B280" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C280" s="19"/>
-    </row>
-    <row r="281" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A281" s="13">
-        <v>1</v>
-      </c>
-      <c r="B281" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C281" s="17"/>
-    </row>
-    <row r="282" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A282" s="12">
-        <v>1</v>
-      </c>
-      <c r="B282" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C282" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A283" s="13">
-        <v>1</v>
-      </c>
-      <c r="B283" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C283" s="17"/>
-    </row>
-    <row r="284" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A284" s="12">
-        <v>3</v>
-      </c>
-      <c r="B284" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C284" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A285" s="13">
-        <v>2</v>
-      </c>
-      <c r="B285" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C285" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A286" s="12">
-        <v>3</v>
-      </c>
-      <c r="B286" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C286" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A287" s="13">
-        <v>1</v>
-      </c>
-      <c r="B287" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C287" s="17"/>
-    </row>
-    <row r="288" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A288" s="12">
-        <v>1</v>
-      </c>
-      <c r="B288" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C288" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A289" s="13">
-        <v>2</v>
-      </c>
-      <c r="B289" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C289" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A290" s="12">
-        <v>1</v>
-      </c>
-      <c r="B290" s="19"/>
-      <c r="C290" s="19"/>
-    </row>
-    <row r="291" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A291" s="13">
-        <v>2</v>
-      </c>
-      <c r="B291" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C291" s="17"/>
-    </row>
-    <row r="292" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A292" s="12">
-        <v>2</v>
-      </c>
-      <c r="B292" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C292" s="19"/>
-    </row>
-    <row r="293" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A293" s="13">
-        <v>2</v>
-      </c>
-      <c r="B293" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C293" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A294" s="12">
-        <v>1</v>
-      </c>
-      <c r="B294" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C294" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="13">
-        <v>1</v>
-      </c>
-      <c r="B295" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C295" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A296" s="12">
-        <v>1</v>
-      </c>
-      <c r="B296" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C296" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A297" s="13">
-        <v>2</v>
-      </c>
-      <c r="B297" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C297" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A298" s="12">
-        <v>2</v>
-      </c>
-      <c r="B298" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C298" s="19"/>
-    </row>
-    <row r="299" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A299" s="13">
-        <v>1</v>
-      </c>
-      <c r="B299" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C299" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A300" s="12">
-        <v>2</v>
-      </c>
-      <c r="B300" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C300" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A301" s="13">
-        <v>2</v>
-      </c>
-      <c r="B301" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C301" s="17"/>
-    </row>
-    <row r="302" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="12">
-        <v>2</v>
-      </c>
-      <c r="B302" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C302" s="19"/>
-    </row>
-    <row r="303" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A303" s="13">
-        <v>3</v>
-      </c>
-      <c r="B303" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C303" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A304" s="12">
-        <v>2</v>
-      </c>
-      <c r="B304" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C304" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A305" s="13">
-        <v>2</v>
-      </c>
-      <c r="B305" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C305" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A306" s="12">
-        <v>1</v>
-      </c>
-      <c r="B306" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C306" s="19"/>
-    </row>
-    <row r="307" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A307" s="13">
-        <v>1</v>
-      </c>
-      <c r="B307" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C307" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A308" s="12">
-        <v>2</v>
-      </c>
-      <c r="B308" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C308" s="19"/>
-    </row>
-    <row r="309" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A309" s="13">
-        <v>2</v>
-      </c>
-      <c r="B309" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C309" s="17"/>
-    </row>
-    <row r="310" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A310" s="12">
-        <v>3</v>
-      </c>
-      <c r="B310" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C310" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A311" s="13">
-        <v>2</v>
-      </c>
-      <c r="B311" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C311" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A312" s="12">
-        <v>2</v>
-      </c>
-      <c r="B312" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C312" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A313" s="13">
-        <v>2</v>
-      </c>
-      <c r="B313" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C313" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A314" s="12">
-        <v>1</v>
-      </c>
-      <c r="B314" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C314" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A315" s="13">
-        <v>2</v>
-      </c>
-      <c r="B315" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C315" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A316" s="12">
-        <v>1</v>
-      </c>
-      <c r="B316" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C316" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A317" s="13">
-        <v>3</v>
-      </c>
-      <c r="B317" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C317" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A318" s="12">
-        <v>2</v>
-      </c>
-      <c r="B318" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C318" s="19"/>
-    </row>
-    <row r="319" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A319" s="13">
-        <v>2</v>
-      </c>
-      <c r="B319" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C319" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A320" s="12">
-        <v>2</v>
-      </c>
-      <c r="B320" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C320" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A321" s="13">
-        <v>3</v>
-      </c>
-      <c r="B321" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C321" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A322" s="12">
-        <v>2</v>
-      </c>
-      <c r="B322" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C322" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A323" s="13">
-        <v>2</v>
-      </c>
-      <c r="B323" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C323" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A324" s="12">
-        <v>1</v>
-      </c>
-      <c r="B324" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C324" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A325" s="13">
-        <v>2</v>
-      </c>
-      <c r="B325" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C325" s="17"/>
-    </row>
-    <row r="326" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A326" s="12">
-        <v>1</v>
-      </c>
-      <c r="B326" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C326" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A327" s="13">
-        <v>2</v>
-      </c>
-      <c r="B327" s="17"/>
-      <c r="C327" s="17"/>
-    </row>
-    <row r="328" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A328" s="12">
-        <v>1</v>
-      </c>
-      <c r="B328" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C328" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A329" s="13">
-        <v>2</v>
-      </c>
-      <c r="B329" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C329" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A330" s="12">
-        <v>1</v>
-      </c>
-      <c r="B330" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C330" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A331" s="13">
-        <v>1</v>
-      </c>
-      <c r="B331" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C331" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A332" s="12">
-        <v>3</v>
-      </c>
-      <c r="B332" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C332" s="19"/>
-    </row>
-    <row r="333" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A333" s="13">
-        <v>2</v>
-      </c>
-      <c r="B333" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C333" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A334" s="12">
-        <v>1</v>
-      </c>
-      <c r="B334" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C334" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A335" s="13">
-        <v>3</v>
-      </c>
-      <c r="B335" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C335" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A336" s="12">
-        <v>2</v>
-      </c>
-      <c r="B336" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C336" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A337" s="13">
-        <v>3</v>
-      </c>
-      <c r="B337" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C337" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A338" s="12">
-        <v>3</v>
-      </c>
-      <c r="B338" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C338" s="19"/>
-    </row>
-    <row r="339" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A339" s="13">
-        <v>1</v>
-      </c>
-      <c r="B339" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C339" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A340" s="12">
-        <v>1</v>
-      </c>
-      <c r="B340" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C340" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A341" s="13">
-        <v>1</v>
-      </c>
-      <c r="B341" s="17"/>
-      <c r="C341" s="17"/>
-    </row>
-    <row r="342" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A342" s="12">
-        <v>2</v>
-      </c>
-      <c r="B342" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C342" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A343" s="13">
-        <v>3</v>
-      </c>
-      <c r="B343" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C343" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A344" s="12">
-        <v>1</v>
-      </c>
-      <c r="B344" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C344" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A345" s="13">
-        <v>3</v>
-      </c>
-      <c r="B345" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C345" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A346" s="12">
-        <v>2</v>
-      </c>
-      <c r="B346" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C346" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A347" s="13">
-        <v>1</v>
-      </c>
-      <c r="B347" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C347" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A348" s="12">
-        <v>3</v>
-      </c>
-      <c r="B348" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C348" s="19"/>
-    </row>
-    <row r="349" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A349" s="13">
-        <v>2</v>
-      </c>
-      <c r="B349" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C349" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A350" s="12">
-        <v>2</v>
-      </c>
-      <c r="B350" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C350" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A351" s="13">
-        <v>1</v>
-      </c>
-      <c r="B351" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C351" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A352" s="12">
-        <v>1</v>
-      </c>
-      <c r="B352" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C352" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A353" s="13">
-        <v>2</v>
-      </c>
-      <c r="B353" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C353" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A354" s="12">
-        <v>1</v>
-      </c>
-      <c r="B354" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C354" s="19"/>
-    </row>
-    <row r="355" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A355" s="13">
-        <v>2</v>
-      </c>
-      <c r="B355" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C355" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A356" s="12">
-        <v>2</v>
-      </c>
-      <c r="B356" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C356" s="19"/>
-    </row>
-    <row r="357" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A357" s="13">
-        <v>2</v>
-      </c>
-      <c r="B357" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C357" s="17"/>
-    </row>
-    <row r="358" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A358" s="12">
-        <v>2</v>
-      </c>
-      <c r="B358" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C358" s="19"/>
-    </row>
-    <row r="359" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A359" s="13">
-        <v>1</v>
-      </c>
-      <c r="B359" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C359" s="17"/>
-    </row>
-    <row r="360" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A360" s="12">
-        <v>2</v>
-      </c>
-      <c r="B360" s="19"/>
-      <c r="C360" s="19"/>
-    </row>
-    <row r="361" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A361" s="13">
-        <v>1</v>
-      </c>
-      <c r="B361" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C361" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A362" s="12">
-        <v>2</v>
-      </c>
-      <c r="B362" s="19"/>
-      <c r="C362" s="19"/>
-    </row>
-    <row r="363" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A363" s="13">
-        <v>1</v>
-      </c>
-      <c r="B363" s="17"/>
-      <c r="C363" s="17"/>
-    </row>
-    <row r="364" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A364" s="12">
-        <v>2</v>
-      </c>
-      <c r="B364" s="19"/>
-      <c r="C364" s="19"/>
-    </row>
-    <row r="365" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A365" s="13">
-        <v>2</v>
-      </c>
-      <c r="B365" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C365" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A366" s="12">
-        <v>1</v>
-      </c>
-      <c r="B366" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C366" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A367" s="13">
-        <v>2</v>
-      </c>
-      <c r="B367" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C367" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A368" s="12">
-        <v>1</v>
-      </c>
-      <c r="B368" s="19"/>
-      <c r="C368" s="19"/>
-    </row>
-    <row r="369" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A369" s="13">
-        <v>1</v>
-      </c>
-      <c r="B369" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C369" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A370" s="12">
-        <v>1</v>
-      </c>
-      <c r="B370" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C370" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A371" s="13">
-        <v>2</v>
-      </c>
-      <c r="B371" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C371" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A372" s="12">
-        <v>2</v>
-      </c>
-      <c r="B372" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C372" s="19"/>
-    </row>
-    <row r="373" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A373" s="13">
-        <v>1</v>
-      </c>
-      <c r="B373" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C373" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A374" s="12">
-        <v>3</v>
-      </c>
-      <c r="B374" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C374" s="19"/>
-    </row>
-    <row r="375" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A375" s="13">
-        <v>2</v>
-      </c>
-      <c r="B375" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C375" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A376" s="12">
-        <v>2</v>
-      </c>
-      <c r="B376" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C376" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A377" s="13">
-        <v>2</v>
-      </c>
-      <c r="B377" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C377" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A378" s="12">
-        <v>1</v>
-      </c>
-      <c r="B378" s="19"/>
-      <c r="C378" s="19"/>
-    </row>
-    <row r="379" spans="1:3" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A379" s="13">
-        <v>1</v>
-      </c>
-      <c r="B379" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C379" s="17"/>
-    </row>
-    <row r="380" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A380" s="12">
-        <v>3</v>
-      </c>
-      <c r="B380" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C380" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A381" s="13">
-        <v>1</v>
-      </c>
-      <c r="B381" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C381" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A382" s="12">
-        <v>1</v>
-      </c>
-      <c r="B382" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C382" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A383" s="13">
-        <v>2</v>
-      </c>
-      <c r="B383" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C383" s="17"/>
-    </row>
-    <row r="384" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A384" s="12">
-        <v>3</v>
-      </c>
-      <c r="B384" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C384" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A385" s="13">
-        <v>1</v>
-      </c>
-      <c r="B385" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C385" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A386" s="12">
-        <v>2</v>
-      </c>
-      <c r="B386" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C386" s="19"/>
-    </row>
-    <row r="387" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A387" s="13">
-        <v>1</v>
-      </c>
-      <c r="B387" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C387" s="17"/>
-    </row>
-    <row r="388" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A388" s="12">
-        <v>1</v>
-      </c>
-      <c r="B388" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C388" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A389" s="13">
-        <v>1</v>
-      </c>
-      <c r="B389" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C389" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A390" s="12">
-        <v>2</v>
-      </c>
-      <c r="B390" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C390" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A391" s="13">
-        <v>2</v>
-      </c>
-      <c r="B391" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C391" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A392" s="12">
-        <v>3</v>
-      </c>
-      <c r="B392" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C392" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A393" s="13">
-        <v>1</v>
-      </c>
-      <c r="B393" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C393" s="17"/>
-    </row>
-    <row r="394" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A394" s="12">
-        <v>2</v>
-      </c>
-      <c r="B394" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C394" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A395" s="13">
-        <v>2</v>
-      </c>
-      <c r="B395" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C395" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A396" s="12">
-        <v>3</v>
-      </c>
-      <c r="B396" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C396" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A397" s="13">
-        <v>1</v>
-      </c>
-      <c r="B397" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C397" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A398" s="12">
-        <v>3</v>
-      </c>
-      <c r="B398" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C398" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A399" s="13">
-        <v>2</v>
-      </c>
-      <c r="B399" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C399" s="17"/>
-    </row>
-    <row r="400" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A400" s="12">
-        <v>2</v>
-      </c>
-      <c r="B400" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C400" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A401" s="13">
-        <v>2</v>
-      </c>
-      <c r="B401" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C401" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A402" s="12">
-        <v>2</v>
-      </c>
-      <c r="B402" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C402" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A403" s="13">
-        <v>2</v>
-      </c>
-      <c r="B403" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C403" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A404" s="12">
-        <v>2</v>
-      </c>
-      <c r="B404" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C404" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A405" s="13">
-        <v>1</v>
-      </c>
-      <c r="B405" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C405" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A406" s="12">
-        <v>3</v>
-      </c>
-      <c r="B406" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C406" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A407" s="13">
-        <v>2</v>
-      </c>
-      <c r="B407" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C407" s="17"/>
-    </row>
-    <row r="408" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A408" s="12">
-        <v>1</v>
-      </c>
-      <c r="B408" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C408" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A409" s="13">
-        <v>2</v>
-      </c>
-      <c r="B409" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C409" s="17"/>
-    </row>
-    <row r="410" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A410" s="12">
-        <v>1</v>
-      </c>
-      <c r="B410" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C410" s="19"/>
-    </row>
-    <row r="411" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A411" s="13">
-        <v>2</v>
-      </c>
-      <c r="B411" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C411" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A412" s="12">
-        <v>2</v>
-      </c>
-      <c r="B412" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C412" s="19"/>
-    </row>
-    <row r="413" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A413" s="13">
-        <v>2</v>
-      </c>
-      <c r="B413" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C413" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A414" s="12">
-        <v>1</v>
-      </c>
-      <c r="B414" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C414" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A415" s="13">
-        <v>1</v>
-      </c>
-      <c r="B415" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C415" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A416" s="12">
-        <v>3</v>
-      </c>
-      <c r="B416" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C416" s="19"/>
-    </row>
-    <row r="417" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A417" s="13">
-        <v>2</v>
-      </c>
-      <c r="B417" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C417" s="17"/>
-    </row>
-    <row r="418" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A418" s="12">
-        <v>2</v>
-      </c>
-      <c r="B418" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C418" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A419" s="13">
-        <v>2</v>
-      </c>
-      <c r="B419" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C419" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A420" s="12">
-        <v>1</v>
-      </c>
-      <c r="B420" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C420" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A421" s="13">
-        <v>2</v>
-      </c>
-      <c r="B421" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C421" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A422" s="12">
-        <v>2</v>
-      </c>
-      <c r="B422" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C422" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A423" s="13">
-        <v>3</v>
-      </c>
-      <c r="B423" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C423" s="17"/>
-    </row>
-    <row r="424" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A424" s="12">
-        <v>1</v>
-      </c>
-      <c r="B424" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C424" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A425" s="13">
-        <v>2</v>
-      </c>
-      <c r="B425" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C425" s="17"/>
-    </row>
-    <row r="426" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A426" s="12">
-        <v>1</v>
-      </c>
-      <c r="B426" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C426" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A427" s="13">
-        <v>2</v>
-      </c>
-      <c r="B427" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C427" s="17"/>
-    </row>
-    <row r="428" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A428" s="12">
-        <v>3</v>
-      </c>
-      <c r="B428" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C428" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A429" s="13">
-        <v>2</v>
-      </c>
-      <c r="B429" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C429" s="17"/>
-    </row>
-    <row r="430" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A430" s="12">
-        <v>2</v>
-      </c>
-      <c r="B430" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C430" s="19"/>
-    </row>
-    <row r="431" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A431" s="13">
-        <v>2</v>
-      </c>
-      <c r="B431" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C431" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A432" s="12">
-        <v>1</v>
-      </c>
-      <c r="B432" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C432" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A433" s="13">
-        <v>1</v>
-      </c>
-      <c r="B433" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C433" s="17"/>
-    </row>
-    <row r="434" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A434" s="12">
-        <v>2</v>
-      </c>
-      <c r="B434" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C434" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A435" s="13">
-        <v>1</v>
-      </c>
-      <c r="B435" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C435" s="17"/>
-    </row>
-    <row r="436" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A436" s="12">
-        <v>1</v>
-      </c>
-      <c r="B436" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C436" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A437" s="13">
-        <v>2</v>
-      </c>
-      <c r="B437" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C437" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A438" s="12">
-        <v>1</v>
-      </c>
-      <c r="B438" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C438" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A439" s="13">
-        <v>2</v>
-      </c>
-      <c r="B439" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C439" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A440" s="12">
-        <v>1</v>
-      </c>
-      <c r="B440" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C440" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A441" s="13">
-        <v>1</v>
-      </c>
-      <c r="B441" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C441" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A442" s="12">
-        <v>2</v>
-      </c>
-      <c r="B442" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C442" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A443" s="13">
-        <v>1</v>
-      </c>
-      <c r="B443" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C443" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A444" s="12">
-        <v>2</v>
-      </c>
-      <c r="B444" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C444" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A445" s="13">
-        <v>1</v>
-      </c>
-      <c r="B445" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C445" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A446" s="12">
-        <v>2</v>
-      </c>
-      <c r="B446" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C446" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A447" s="13">
-        <v>2</v>
-      </c>
-      <c r="B447" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C447" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A448" s="12">
-        <v>2</v>
-      </c>
-      <c r="B448" s="19"/>
-      <c r="C448" s="19"/>
-    </row>
-    <row r="449" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A449" s="13">
-        <v>2</v>
-      </c>
-      <c r="B449" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C449" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A450" s="12">
-        <v>3</v>
-      </c>
-      <c r="B450" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C450" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A451" s="13">
-        <v>2</v>
-      </c>
-      <c r="B451" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C451" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A452" s="12">
-        <v>1</v>
-      </c>
-      <c r="B452" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C452" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A453" s="13">
-        <v>2</v>
-      </c>
-      <c r="B453" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C453" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A454" s="12">
-        <v>1</v>
-      </c>
-      <c r="B454" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C454" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A455" s="13">
-        <v>3</v>
-      </c>
-      <c r="B455" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C455" s="17"/>
-    </row>
-    <row r="456" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A456" s="12">
-        <v>3</v>
-      </c>
-      <c r="B456" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C456" s="19"/>
-    </row>
-    <row r="457" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A457" s="13">
-        <v>1</v>
-      </c>
-      <c r="B457" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C457" s="17"/>
-    </row>
-    <row r="458" spans="1:3" ht="78.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A458" s="12">
-        <v>1</v>
-      </c>
-      <c r="B458" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C458" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A459" s="13">
-        <v>1</v>
-      </c>
-      <c r="B459" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C459" s="17"/>
-    </row>
-    <row r="460" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A460" s="12">
-        <v>1</v>
-      </c>
-      <c r="B460" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C460" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A461" s="13">
-        <v>1</v>
-      </c>
-      <c r="B461" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C461" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A462" s="12">
-        <v>1</v>
-      </c>
-      <c r="B462" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C462" s="19"/>
-    </row>
-    <row r="463" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A463" s="13">
-        <v>1</v>
-      </c>
-      <c r="B463" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C463" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A464" s="12">
-        <v>1</v>
-      </c>
-      <c r="B464" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C464" s="19"/>
-    </row>
-    <row r="465" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A465" s="13">
-        <v>2</v>
-      </c>
-      <c r="B465" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C465" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A466" s="12">
-        <v>1</v>
-      </c>
-      <c r="B466" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C466" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A467" s="13">
-        <v>2</v>
-      </c>
-      <c r="B467" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C467" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A468" s="12">
-        <v>2</v>
-      </c>
-      <c r="B468" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C468" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A469" s="13">
-        <v>1</v>
-      </c>
-      <c r="B469" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C469" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A470" s="12">
-        <v>1</v>
-      </c>
-      <c r="B470" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C470" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A471" s="13">
-        <v>1</v>
-      </c>
-      <c r="B471" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C471" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="104.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A472" s="12">
-        <v>2</v>
-      </c>
-      <c r="B472" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C472" s="19"/>
-    </row>
-    <row r="473" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A473" s="13">
-        <v>1</v>
-      </c>
-      <c r="B473" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C473" s="17"/>
-    </row>
-    <row r="474" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A474" s="12">
-        <v>1</v>
-      </c>
-      <c r="B474" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C474" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A475" s="13">
-        <v>2</v>
-      </c>
-      <c r="B475" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C475" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A476" s="12">
-        <v>3</v>
-      </c>
-      <c r="B476" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C476" s="19"/>
-    </row>
-    <row r="477" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A477" s="13">
-        <v>1</v>
-      </c>
-      <c r="B477" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C477" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A478" s="12">
-        <v>1</v>
-      </c>
-      <c r="B478" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C478" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A479" s="13">
-        <v>1</v>
-      </c>
-      <c r="B479" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C479" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A480" s="12">
-        <v>1</v>
-      </c>
-      <c r="B480" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C480" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A481" s="13">
-        <v>1</v>
-      </c>
-      <c r="B481" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C481" s="17"/>
-    </row>
-    <row r="482" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A482" s="12">
-        <v>1</v>
-      </c>
-      <c r="B482" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C482" s="19"/>
-    </row>
-    <row r="483" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A483" s="13">
-        <v>1</v>
-      </c>
-      <c r="B483" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C483" s="17"/>
-    </row>
-    <row r="484" spans="1:3" ht="91.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A484" s="12">
-        <v>2</v>
-      </c>
-      <c r="B484" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C484" s="19"/>
-    </row>
-    <row r="485" spans="1:3" ht="143.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A485" s="13">
-        <v>1</v>
-      </c>
-      <c r="B485" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C485" s="17"/>
+      <c r="C484" s="17"/>
+    </row>
+    <row r="485" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A485" s="12">
+        <v>1</v>
+      </c>
+      <c r="B485" s="15">
+        <v>1</v>
+      </c>
+      <c r="C485" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="486" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A486" s="12">
-        <v>1</v>
-      </c>
-      <c r="B486" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C486" s="12">
+      <c r="A486" s="13">
+        <v>3</v>
+      </c>
+      <c r="B486" s="16">
+        <v>1</v>
+      </c>
+      <c r="C486" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A487" s="13">
-        <v>3</v>
-      </c>
-      <c r="B487" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C487" s="13">
+      <c r="A487" s="12">
+        <v>1</v>
+      </c>
+      <c r="B487" s="15">
+        <v>1</v>
+      </c>
+      <c r="C487" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A488" s="12">
-        <v>1</v>
-      </c>
-      <c r="B488" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C488" s="12">
+      <c r="A488" s="13">
+        <v>3</v>
+      </c>
+      <c r="B488" s="16">
+        <v>1</v>
+      </c>
+      <c r="C488" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A489" s="13">
-        <v>3</v>
-      </c>
-      <c r="B489" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C489" s="13">
+      <c r="A489" s="12">
+        <v>1</v>
+      </c>
+      <c r="B489" s="15">
+        <v>1</v>
+      </c>
+      <c r="C489" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A490" s="12">
-        <v>1</v>
-      </c>
-      <c r="B490" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C490" s="12">
+      <c r="A490" s="13">
+        <v>1</v>
+      </c>
+      <c r="B490" s="16">
+        <v>1</v>
+      </c>
+      <c r="C490" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A491" s="13">
-        <v>1</v>
-      </c>
-      <c r="B491" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C491" s="13">
+      <c r="A491" s="12">
+        <v>1</v>
+      </c>
+      <c r="B491" s="15">
+        <v>1</v>
+      </c>
+      <c r="C491" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A492" s="12">
-        <v>1</v>
-      </c>
-      <c r="B492" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C492" s="12">
+      <c r="A492" s="13">
+        <v>1</v>
+      </c>
+      <c r="B492" s="16">
+        <v>1</v>
+      </c>
+      <c r="C492" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A493" s="13">
-        <v>1</v>
-      </c>
-      <c r="B493" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C493" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A494" s="14">
-        <v>3</v>
-      </c>
-      <c r="B494" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C494" s="14">
+      <c r="A493" s="14">
+        <v>3</v>
+      </c>
+      <c r="B493" s="18">
+        <v>1</v>
+      </c>
+      <c r="C493" s="14">
         <v>1</v>
       </c>
     </row>
